--- a/calculations/calculate.xlsx
+++ b/calculations/calculate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_WORK\Code\Rust\ternary-contours\calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F64E75-0BBD-4D7E-80DA-53701069CB84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D994F94-34F3-46D3-A83D-E4A75A363593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-51720" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{469B9D63-5433-41F2-A00C-660877644039}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="9">
   <si>
     <t>Lime.T</t>
   </si>
@@ -438,14 +438,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{468ADC57-9496-402C-AEE2-C85FEC6357C2}">
-  <dimension ref="B3:M69"/>
+  <dimension ref="B3:Z234"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -479,8 +481,32 @@
       <c r="M3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X3" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B4">
         <v>0</v>
       </c>
@@ -514,8 +540,32 @@
       <c r="M4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S4">
+        <v>1000</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>1</v>
+      </c>
+      <c r="X4" s="1">
+        <v>1437.3077000000001</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>1974.8418999999999</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B5">
         <v>0</v>
       </c>
@@ -549,8 +599,32 @@
       <c r="M5">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S5">
+        <v>1000</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0.05</v>
+      </c>
+      <c r="W5">
+        <v>0.95</v>
+      </c>
+      <c r="X5" s="1">
+        <v>1405.7385999999999</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>1938.4637</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>234.75817000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B6">
         <v>0</v>
       </c>
@@ -584,8 +658,32 @@
       <c r="M6">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S6">
+        <v>1000</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0.1</v>
+      </c>
+      <c r="W6">
+        <v>0.9</v>
+      </c>
+      <c r="X6" s="1">
+        <v>1375.5567000000001</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>1904.0459000000001</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>337.93394999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B7">
         <v>0</v>
       </c>
@@ -619,8 +717,32 @@
       <c r="M7">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S7">
+        <v>1000</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0.15</v>
+      </c>
+      <c r="W7">
+        <v>0.85</v>
+      </c>
+      <c r="X7" s="1">
+        <v>1345.9626000000001</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>1870.4997000000001</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>409.39537999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>0</v>
       </c>
@@ -654,8 +776,32 @@
       <c r="M8">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S8">
+        <v>1000</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0.2</v>
+      </c>
+      <c r="W8">
+        <v>0.8</v>
+      </c>
+      <c r="X8" s="1">
+        <v>1316.4404999999999</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>1837.1670999999999</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>464.92631</v>
+      </c>
+    </row>
+    <row r="9" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B9">
         <v>0</v>
       </c>
@@ -689,8 +835,32 @@
       <c r="M9">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S9">
+        <v>1000</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0.25</v>
+      </c>
+      <c r="W9">
+        <v>0.75</v>
+      </c>
+      <c r="X9" s="1">
+        <v>1286.5947000000001</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>1803.568</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>510.66681999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>0</v>
       </c>
@@ -724,8 +894,32 @@
       <c r="M10">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S10">
+        <v>1000</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0.3</v>
+      </c>
+      <c r="W10">
+        <v>0.7</v>
+      </c>
+      <c r="X10" s="1">
+        <v>1256.0763999999999</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>1769.2973</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>549.79620999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B11">
         <v>0</v>
       </c>
@@ -759,8 +953,32 @@
       <c r="M11">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S11">
+        <v>1000</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0.35</v>
+      </c>
+      <c r="W11">
+        <v>0.65</v>
+      </c>
+      <c r="X11" s="1">
+        <v>1224.5436999999999</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>1733.9701</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>584.20615999999995</v>
+      </c>
+    </row>
+    <row r="12" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B12">
         <v>0</v>
       </c>
@@ -794,8 +1012,32 @@
       <c r="M12">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S12">
+        <v>1000</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0.4</v>
+      </c>
+      <c r="W12">
+        <v>0.6</v>
+      </c>
+      <c r="X12" s="1">
+        <v>1191.6314</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>1697.1858999999999</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>615.12239999999997</v>
+      </c>
+    </row>
+    <row r="13" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B13">
         <v>0</v>
       </c>
@@ -829,8 +1071,32 @@
       <c r="M13">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S13">
+        <v>1000</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0.45</v>
+      </c>
+      <c r="W13">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="X13" s="1">
+        <v>1156.9246000000001</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>1658.4972</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>643.38792999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B14">
         <v>0</v>
       </c>
@@ -864,8 +1130,32 @@
       <c r="M14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S14">
+        <v>1000</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0.5</v>
+      </c>
+      <c r="W14">
+        <v>0.5</v>
+      </c>
+      <c r="X14" s="1">
+        <v>1119.9277</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>1617.3761</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>669.60937999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B15">
         <v>0.1</v>
       </c>
@@ -899,8 +1189,32 @@
       <c r="M15">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S15">
+        <v>1000</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="W15">
+        <v>0.45</v>
+      </c>
+      <c r="X15" s="1">
+        <v>1080.0236</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>1573.1704</v>
+      </c>
+      <c r="Z15" s="1">
+        <v>694.23951999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B16">
         <v>0.1</v>
       </c>
@@ -934,8 +1248,32 @@
       <c r="M16">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S16">
+        <v>1000</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0.6</v>
+      </c>
+      <c r="W16">
+        <v>0.4</v>
+      </c>
+      <c r="X16" s="1">
+        <v>1036.4141999999999</v>
+      </c>
+      <c r="Y16" s="1">
+        <v>1525.0405000000001</v>
+      </c>
+      <c r="Z16" s="1">
+        <v>717.62697000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B17">
         <v>0.1</v>
       </c>
@@ -969,8 +1307,32 @@
       <c r="M17">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S17">
+        <v>1000</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0.65</v>
+      </c>
+      <c r="W17">
+        <v>0.35</v>
+      </c>
+      <c r="X17" s="1">
+        <v>988.02677000000006</v>
+      </c>
+      <c r="Y17" s="1">
+        <v>1471.8605</v>
+      </c>
+      <c r="Z17" s="1">
+        <v>740.04794000000004</v>
+      </c>
+    </row>
+    <row r="18" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B18">
         <v>0.1</v>
       </c>
@@ -1004,8 +1366,32 @@
       <c r="M18">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S18">
+        <v>1000</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0.7</v>
+      </c>
+      <c r="W18">
+        <v>0.3</v>
+      </c>
+      <c r="X18" s="1">
+        <v>933.35631999999998</v>
+      </c>
+      <c r="Y18" s="1">
+        <v>1412.0507</v>
+      </c>
+      <c r="Z18" s="1">
+        <v>761.72753999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B19">
         <v>0.1</v>
       </c>
@@ -1039,8 +1425,32 @@
       <c r="M19">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S19">
+        <v>1000</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0.75</v>
+      </c>
+      <c r="W19">
+        <v>0.25</v>
+      </c>
+      <c r="X19" s="1">
+        <v>870.18152999999995</v>
+      </c>
+      <c r="Y19" s="1">
+        <v>1343.2724000000001</v>
+      </c>
+      <c r="Z19" s="1">
+        <v>782.85515999999996</v>
+      </c>
+    </row>
+    <row r="20" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B20">
         <v>0.1</v>
       </c>
@@ -1074,8 +1484,32 @@
       <c r="M20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S20">
+        <v>1000</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0.8</v>
+      </c>
+      <c r="W20">
+        <v>0.2</v>
+      </c>
+      <c r="X20" s="1">
+        <v>795.00311999999997</v>
+      </c>
+      <c r="Y20" s="1">
+        <v>1261.817</v>
+      </c>
+      <c r="Z20" s="1">
+        <v>803.59652000000006</v>
+      </c>
+    </row>
+    <row r="21" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B21">
         <v>0.1</v>
       </c>
@@ -1109,8 +1543,32 @@
       <c r="M21">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S21">
+        <v>1000</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0.85</v>
+      </c>
+      <c r="W21">
+        <v>0.15</v>
+      </c>
+      <c r="X21" s="1">
+        <v>701.78949999999998</v>
+      </c>
+      <c r="Y21" s="1">
+        <v>1161.2102</v>
+      </c>
+      <c r="Z21" s="1">
+        <v>824.10455000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B22">
         <v>0.1</v>
       </c>
@@ -1144,8 +1602,32 @@
       <c r="M22">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S22">
+        <v>1000</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0.9</v>
+      </c>
+      <c r="W22">
+        <v>0.1</v>
+      </c>
+      <c r="X22" s="1">
+        <v>578.58272999999997</v>
+      </c>
+      <c r="Y22" s="1">
+        <v>1028.3202000000001</v>
+      </c>
+      <c r="Z22" s="1">
+        <v>844.53123000000005</v>
+      </c>
+    </row>
+    <row r="23" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B23">
         <v>0.1</v>
       </c>
@@ -1179,8 +1661,32 @@
       <c r="M23">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S23">
+        <v>1000</v>
+      </c>
+      <c r="T23">
+        <v>1</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0.95</v>
+      </c>
+      <c r="W23">
+        <v>0.05</v>
+      </c>
+      <c r="X23" s="1">
+        <v>394.29876000000002</v>
+      </c>
+      <c r="Y23" s="1">
+        <v>827.59464000000003</v>
+      </c>
+      <c r="Z23" s="1">
+        <v>865.04372000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B24">
         <v>0.1</v>
       </c>
@@ -1214,8 +1720,32 @@
       <c r="M24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S24">
+        <v>1000</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>1</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z24" s="1">
+        <v>885.85145999999997</v>
+      </c>
+    </row>
+    <row r="25" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B25">
         <v>0.2</v>
       </c>
@@ -1249,8 +1779,32 @@
       <c r="M25">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S25">
+        <v>1000</v>
+      </c>
+      <c r="T25">
+        <v>1</v>
+      </c>
+      <c r="U25">
+        <v>0.05</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0.95</v>
+      </c>
+      <c r="X25" s="1">
+        <v>1420.3001999999999</v>
+      </c>
+      <c r="Y25" s="1">
+        <v>1936.4595999999999</v>
+      </c>
+      <c r="Z25" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B26">
         <v>0.2</v>
       </c>
@@ -1284,8 +1838,32 @@
       <c r="M26">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S26">
+        <v>1000</v>
+      </c>
+      <c r="T26">
+        <v>1</v>
+      </c>
+      <c r="U26">
+        <v>0.05</v>
+      </c>
+      <c r="V26">
+        <v>0.05</v>
+      </c>
+      <c r="W26">
+        <v>0.9</v>
+      </c>
+      <c r="X26" s="1">
+        <v>1386.4648</v>
+      </c>
+      <c r="Y26" s="1">
+        <v>1896.9784999999999</v>
+      </c>
+      <c r="Z26" s="1">
+        <v>255.37822</v>
+      </c>
+    </row>
+    <row r="27" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B27">
         <v>0.2</v>
       </c>
@@ -1319,8 +1897,32 @@
       <c r="M27">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S27">
+        <v>1000</v>
+      </c>
+      <c r="T27">
+        <v>1</v>
+      </c>
+      <c r="U27">
+        <v>0.05</v>
+      </c>
+      <c r="V27">
+        <v>0.1</v>
+      </c>
+      <c r="W27">
+        <v>0.85</v>
+      </c>
+      <c r="X27" s="1">
+        <v>1354.4784999999999</v>
+      </c>
+      <c r="Y27" s="1">
+        <v>1860.0461</v>
+      </c>
+      <c r="Z27" s="1">
+        <v>358.81209999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B28">
         <v>0.2</v>
       </c>
@@ -1354,8 +1956,32 @@
       <c r="M28">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S28">
+        <v>1000</v>
+      </c>
+      <c r="T28">
+        <v>1</v>
+      </c>
+      <c r="U28">
+        <v>0.05</v>
+      </c>
+      <c r="V28">
+        <v>0.15</v>
+      </c>
+      <c r="W28">
+        <v>0.8</v>
+      </c>
+      <c r="X28" s="1">
+        <v>1323.2303999999999</v>
+      </c>
+      <c r="Y28" s="1">
+        <v>1824.1688999999999</v>
+      </c>
+      <c r="Z28" s="1">
+        <v>428.90980999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B29">
         <v>0.2</v>
       </c>
@@ -1389,8 +2015,32 @@
       <c r="M29">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S29">
+        <v>1000</v>
+      </c>
+      <c r="T29">
+        <v>1</v>
+      </c>
+      <c r="U29">
+        <v>0.05</v>
+      </c>
+      <c r="V29">
+        <v>0.2</v>
+      </c>
+      <c r="W29">
+        <v>0.75</v>
+      </c>
+      <c r="X29" s="1">
+        <v>1292.0862999999999</v>
+      </c>
+      <c r="Y29" s="1">
+        <v>1788.5427</v>
+      </c>
+      <c r="Z29" s="1">
+        <v>482.58154999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B30">
         <v>0.2</v>
       </c>
@@ -1424,8 +2074,32 @@
       <c r="M30">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S30">
+        <v>1000</v>
+      </c>
+      <c r="T30">
+        <v>1</v>
+      </c>
+      <c r="U30">
+        <v>0.05</v>
+      </c>
+      <c r="V30">
+        <v>0.25</v>
+      </c>
+      <c r="W30">
+        <v>0.7</v>
+      </c>
+      <c r="X30" s="1">
+        <v>1260.5742</v>
+      </c>
+      <c r="Y30" s="1">
+        <v>1752.6016999999999</v>
+      </c>
+      <c r="Z30" s="1">
+        <v>526.32901000000004</v>
+      </c>
+    </row>
+    <row r="31" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B31">
         <v>0.2</v>
       </c>
@@ -1459,8 +2133,32 @@
       <c r="M31">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S31">
+        <v>1000</v>
+      </c>
+      <c r="T31">
+        <v>1</v>
+      </c>
+      <c r="U31">
+        <v>0.05</v>
+      </c>
+      <c r="V31">
+        <v>0.3</v>
+      </c>
+      <c r="W31">
+        <v>0.65</v>
+      </c>
+      <c r="X31" s="1">
+        <v>1228.2793999999999</v>
+      </c>
+      <c r="Y31" s="1">
+        <v>1715.8715</v>
+      </c>
+      <c r="Z31" s="1">
+        <v>563.45509000000004</v>
+      </c>
+    </row>
+    <row r="32" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B32">
         <v>0.2</v>
       </c>
@@ -1494,8 +2192,32 @@
       <c r="M32">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S32">
+        <v>1000</v>
+      </c>
+      <c r="T32">
+        <v>1</v>
+      </c>
+      <c r="U32">
+        <v>0.05</v>
+      </c>
+      <c r="V32">
+        <v>0.35</v>
+      </c>
+      <c r="W32">
+        <v>0.6</v>
+      </c>
+      <c r="X32" s="1">
+        <v>1194.7908</v>
+      </c>
+      <c r="Y32" s="1">
+        <v>1677.8985</v>
+      </c>
+      <c r="Z32" s="1">
+        <v>595.89152999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B33">
         <v>0.2</v>
       </c>
@@ -1529,8 +2251,32 @@
       <c r="M33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S33">
+        <v>1000</v>
+      </c>
+      <c r="T33">
+        <v>1</v>
+      </c>
+      <c r="U33">
+        <v>0.05</v>
+      </c>
+      <c r="V33">
+        <v>0.4</v>
+      </c>
+      <c r="W33">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="X33" s="1">
+        <v>1159.6627000000001</v>
+      </c>
+      <c r="Y33" s="1">
+        <v>1638.2041999999999</v>
+      </c>
+      <c r="Z33" s="1">
+        <v>624.87481000000002</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B34">
         <v>0.3</v>
       </c>
@@ -1564,8 +2310,32 @@
       <c r="M34">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S34">
+        <v>1000</v>
+      </c>
+      <c r="T34">
+        <v>1</v>
+      </c>
+      <c r="U34">
+        <v>0.05</v>
+      </c>
+      <c r="V34">
+        <v>0.45</v>
+      </c>
+      <c r="W34">
+        <v>0.5</v>
+      </c>
+      <c r="X34" s="1">
+        <v>1122.3789999999999</v>
+      </c>
+      <c r="Y34" s="1">
+        <v>1596.2453</v>
+      </c>
+      <c r="Z34" s="1">
+        <v>651.25063</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B35">
         <v>0.3</v>
       </c>
@@ -1599,8 +2369,32 @@
       <c r="M35">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S35">
+        <v>1000</v>
+      </c>
+      <c r="T35">
+        <v>1</v>
+      </c>
+      <c r="U35">
+        <v>0.05</v>
+      </c>
+      <c r="V35">
+        <v>0.5</v>
+      </c>
+      <c r="W35">
+        <v>0.45</v>
+      </c>
+      <c r="X35" s="1">
+        <v>1082.3108</v>
+      </c>
+      <c r="Y35" s="1">
+        <v>1551.3686</v>
+      </c>
+      <c r="Z35" s="1">
+        <v>675.62973</v>
+      </c>
+    </row>
+    <row r="36" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B36">
         <v>0.3</v>
       </c>
@@ -1634,8 +2428,32 @@
       <c r="M36">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S36">
+        <v>1000</v>
+      </c>
+      <c r="T36">
+        <v>1</v>
+      </c>
+      <c r="U36">
+        <v>0.05</v>
+      </c>
+      <c r="V36">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="W36">
+        <v>0.4</v>
+      </c>
+      <c r="X36" s="1">
+        <v>1038.6578999999999</v>
+      </c>
+      <c r="Y36" s="1">
+        <v>1502.7507000000001</v>
+      </c>
+      <c r="Z36" s="1">
+        <v>698.47514999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B37">
         <v>0.3</v>
       </c>
@@ -1669,8 +2487,32 @@
       <c r="M37">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S37">
+        <v>1000</v>
+      </c>
+      <c r="T37">
+        <v>1</v>
+      </c>
+      <c r="U37">
+        <v>0.05</v>
+      </c>
+      <c r="V37">
+        <v>0.6</v>
+      </c>
+      <c r="W37">
+        <v>0.35</v>
+      </c>
+      <c r="X37" s="1">
+        <v>990.36045000000001</v>
+      </c>
+      <c r="Y37" s="1">
+        <v>1449.3067000000001</v>
+      </c>
+      <c r="Z37" s="1">
+        <v>720.15472</v>
+      </c>
+    </row>
+    <row r="38" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B38">
         <v>0.3</v>
       </c>
@@ -1704,8 +2546,32 @@
       <c r="M38">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S38">
+        <v>1000</v>
+      </c>
+      <c r="T38">
+        <v>1</v>
+      </c>
+      <c r="U38">
+        <v>0.05</v>
+      </c>
+      <c r="V38">
+        <v>0.65</v>
+      </c>
+      <c r="W38">
+        <v>0.3</v>
+      </c>
+      <c r="X38" s="1">
+        <v>935.95447999999999</v>
+      </c>
+      <c r="Y38" s="1">
+        <v>1389.5389</v>
+      </c>
+      <c r="Z38" s="1">
+        <v>740.97448999999995</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B39">
         <v>0.3</v>
       </c>
@@ -1739,8 +2605,32 @@
       <c r="M39">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S39">
+        <v>1000</v>
+      </c>
+      <c r="T39">
+        <v>1</v>
+      </c>
+      <c r="U39">
+        <v>0.05</v>
+      </c>
+      <c r="V39">
+        <v>0.7</v>
+      </c>
+      <c r="W39">
+        <v>0.25</v>
+      </c>
+      <c r="X39" s="1">
+        <v>873.31714999999997</v>
+      </c>
+      <c r="Y39" s="1">
+        <v>1321.2651000000001</v>
+      </c>
+      <c r="Z39" s="1">
+        <v>761.20109000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B40">
         <v>0.3</v>
       </c>
@@ -1774,8 +2664,32 @@
       <c r="M40">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S40">
+        <v>1000</v>
+      </c>
+      <c r="T40">
+        <v>1</v>
+      </c>
+      <c r="U40">
+        <v>0.05</v>
+      </c>
+      <c r="V40">
+        <v>0.75</v>
+      </c>
+      <c r="W40">
+        <v>0.2</v>
+      </c>
+      <c r="X40" s="1">
+        <v>799.17487000000006</v>
+      </c>
+      <c r="Y40" s="1">
+        <v>1241.0745999999999</v>
+      </c>
+      <c r="Z40" s="1">
+        <v>781.07789000000002</v>
+      </c>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B41">
         <v>0.3</v>
       </c>
@@ -1809,8 +2723,32 @@
       <c r="M41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S41">
+        <v>1000</v>
+      </c>
+      <c r="T41">
+        <v>1</v>
+      </c>
+      <c r="U41">
+        <v>0.05</v>
+      </c>
+      <c r="V41">
+        <v>0.8</v>
+      </c>
+      <c r="W41">
+        <v>0.15</v>
+      </c>
+      <c r="X41" s="1">
+        <v>708.02453000000003</v>
+      </c>
+      <c r="Y41" s="1">
+        <v>1143.0787</v>
+      </c>
+      <c r="Z41" s="1">
+        <v>800.83871999999997</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B42">
         <v>0.4</v>
       </c>
@@ -1844,8 +2782,32 @@
       <c r="M42">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S42">
+        <v>1000</v>
+      </c>
+      <c r="T42">
+        <v>1</v>
+      </c>
+      <c r="U42">
+        <v>0.05</v>
+      </c>
+      <c r="V42">
+        <v>0.85</v>
+      </c>
+      <c r="W42">
+        <v>0.1</v>
+      </c>
+      <c r="X42" s="1">
+        <v>589.22307999999998</v>
+      </c>
+      <c r="Y42" s="1">
+        <v>1015.3604</v>
+      </c>
+      <c r="Z42" s="1">
+        <v>820.72470999999996</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B43">
         <v>0.4</v>
       </c>
@@ -1879,8 +2841,32 @@
       <c r="M43">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S43">
+        <v>1000</v>
+      </c>
+      <c r="T43">
+        <v>1</v>
+      </c>
+      <c r="U43">
+        <v>0.05</v>
+      </c>
+      <c r="V43">
+        <v>0.9</v>
+      </c>
+      <c r="W43">
+        <v>0.05</v>
+      </c>
+      <c r="X43" s="1">
+        <v>519.15260000000001</v>
+      </c>
+      <c r="Y43" s="1">
+        <v>825.11958000000004</v>
+      </c>
+      <c r="Z43" s="1">
+        <v>841.01751000000002</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B44">
         <v>0.4</v>
       </c>
@@ -1914,8 +2900,32 @@
       <c r="M44">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S44">
+        <v>1000</v>
+      </c>
+      <c r="T44">
+        <v>1</v>
+      </c>
+      <c r="U44">
+        <v>0.05</v>
+      </c>
+      <c r="V44">
+        <v>0.95</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+      <c r="X44" s="1">
+        <v>496.90350000000001</v>
+      </c>
+      <c r="Y44" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z44" s="1">
+        <v>862.16090999999994</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B45">
         <v>0.4</v>
       </c>
@@ -1949,8 +2959,32 @@
       <c r="M45">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S45">
+        <v>1000</v>
+      </c>
+      <c r="T45">
+        <v>1</v>
+      </c>
+      <c r="U45">
+        <v>0.1</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0.9</v>
+      </c>
+      <c r="X45" s="1">
+        <v>1402.0815</v>
+      </c>
+      <c r="Y45" s="1">
+        <v>1892.2927999999999</v>
+      </c>
+      <c r="Z45" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B46">
         <v>0.4</v>
       </c>
@@ -1984,8 +3018,32 @@
       <c r="M46">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S46">
+        <v>1000</v>
+      </c>
+      <c r="T46">
+        <v>1</v>
+      </c>
+      <c r="U46">
+        <v>0.1</v>
+      </c>
+      <c r="V46">
+        <v>0.05</v>
+      </c>
+      <c r="W46">
+        <v>0.85</v>
+      </c>
+      <c r="X46" s="1">
+        <v>1365.9108000000001</v>
+      </c>
+      <c r="Y46" s="1">
+        <v>1849.0998999999999</v>
+      </c>
+      <c r="Z46" s="1">
+        <v>278.52933999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B47">
         <v>0.4</v>
       </c>
@@ -2019,8 +3077,32 @@
       <c r="M47">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S47">
+        <v>1000</v>
+      </c>
+      <c r="T47">
+        <v>1</v>
+      </c>
+      <c r="U47">
+        <v>0.1</v>
+      </c>
+      <c r="V47">
+        <v>0.1</v>
+      </c>
+      <c r="W47">
+        <v>0.8</v>
+      </c>
+      <c r="X47" s="1">
+        <v>1332.2560000000001</v>
+      </c>
+      <c r="Y47" s="1">
+        <v>1809.1495</v>
+      </c>
+      <c r="Z47" s="1">
+        <v>381.68434999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B48">
         <v>0.4</v>
       </c>
@@ -2054,8 +3136,32 @@
       <c r="M48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S48">
+        <v>1000</v>
+      </c>
+      <c r="T48">
+        <v>1</v>
+      </c>
+      <c r="U48">
+        <v>0.1</v>
+      </c>
+      <c r="V48">
+        <v>0.15</v>
+      </c>
+      <c r="W48">
+        <v>0.75</v>
+      </c>
+      <c r="X48" s="1">
+        <v>1299.604</v>
+      </c>
+      <c r="Y48" s="1">
+        <v>1770.5117</v>
+      </c>
+      <c r="Z48" s="1">
+        <v>449.69143000000003</v>
+      </c>
+    </row>
+    <row r="49" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B49">
         <v>0.5</v>
       </c>
@@ -2089,8 +3195,32 @@
       <c r="M49">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S49">
+        <v>1000</v>
+      </c>
+      <c r="T49">
+        <v>1</v>
+      </c>
+      <c r="U49">
+        <v>0.1</v>
+      </c>
+      <c r="V49">
+        <v>0.2</v>
+      </c>
+      <c r="W49">
+        <v>0.7</v>
+      </c>
+      <c r="X49" s="1">
+        <v>1267.1550999999999</v>
+      </c>
+      <c r="Y49" s="1">
+        <v>1732.1895999999999</v>
+      </c>
+      <c r="Z49" s="1">
+        <v>500.72865999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B50">
         <v>0.5</v>
       </c>
@@ -2124,8 +3254,32 @@
       <c r="M50">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S50">
+        <v>1000</v>
+      </c>
+      <c r="T50">
+        <v>1</v>
+      </c>
+      <c r="U50">
+        <v>0.1</v>
+      </c>
+      <c r="V50">
+        <v>0.25</v>
+      </c>
+      <c r="W50">
+        <v>0.65</v>
+      </c>
+      <c r="X50" s="1">
+        <v>1234.3511000000001</v>
+      </c>
+      <c r="Y50" s="1">
+        <v>1693.51</v>
+      </c>
+      <c r="Z50" s="1">
+        <v>541.67903000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B51">
         <v>0.5</v>
       </c>
@@ -2159,8 +3313,32 @@
       <c r="M51">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S51">
+        <v>1000</v>
+      </c>
+      <c r="T51">
+        <v>1</v>
+      </c>
+      <c r="U51">
+        <v>0.1</v>
+      </c>
+      <c r="V51">
+        <v>0.3</v>
+      </c>
+      <c r="W51">
+        <v>0.6</v>
+      </c>
+      <c r="X51" s="1">
+        <v>1200.7158999999999</v>
+      </c>
+      <c r="Y51" s="1">
+        <v>1653.9204</v>
+      </c>
+      <c r="Z51" s="1">
+        <v>575.9683</v>
+      </c>
+    </row>
+    <row r="52" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B52">
         <v>0.5</v>
       </c>
@@ -2194,8 +3372,32 @@
       <c r="M52">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S52">
+        <v>1000</v>
+      </c>
+      <c r="T52">
+        <v>1</v>
+      </c>
+      <c r="U52">
+        <v>0.1</v>
+      </c>
+      <c r="V52">
+        <v>0.35</v>
+      </c>
+      <c r="W52">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="X52" s="1">
+        <v>1165.7791</v>
+      </c>
+      <c r="Y52" s="1">
+        <v>1612.8964000000001</v>
+      </c>
+      <c r="Z52" s="1">
+        <v>605.57227999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B53">
         <v>0.5</v>
       </c>
@@ -2229,8 +3431,32 @@
       <c r="M53">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S53">
+        <v>1000</v>
+      </c>
+      <c r="T53">
+        <v>1</v>
+      </c>
+      <c r="U53">
+        <v>0.1</v>
+      </c>
+      <c r="V53">
+        <v>0.4</v>
+      </c>
+      <c r="W53">
+        <v>0.5</v>
+      </c>
+      <c r="X53" s="1">
+        <v>1129.0245</v>
+      </c>
+      <c r="Y53" s="1">
+        <v>1569.8833999999999</v>
+      </c>
+      <c r="Z53" s="1">
+        <v>631.75322000000006</v>
+      </c>
+    </row>
+    <row r="54" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B54">
         <v>0.5</v>
       </c>
@@ -2264,8 +3490,32 @@
       <c r="M54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S54">
+        <v>1000</v>
+      </c>
+      <c r="T54">
+        <v>1</v>
+      </c>
+      <c r="U54">
+        <v>0.1</v>
+      </c>
+      <c r="V54">
+        <v>0.45</v>
+      </c>
+      <c r="W54">
+        <v>0.45</v>
+      </c>
+      <c r="X54" s="1">
+        <v>1089.8385000000001</v>
+      </c>
+      <c r="Y54" s="1">
+        <v>1524.2452000000001</v>
+      </c>
+      <c r="Z54" s="1">
+        <v>655.38647000000003</v>
+      </c>
+    </row>
+    <row r="55" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B55">
         <v>0.6</v>
       </c>
@@ -2299,8 +3549,32 @@
       <c r="M55">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S55">
+        <v>1000</v>
+      </c>
+      <c r="T55">
+        <v>1</v>
+      </c>
+      <c r="U55">
+        <v>0.1</v>
+      </c>
+      <c r="V55">
+        <v>0.5</v>
+      </c>
+      <c r="W55">
+        <v>0.4</v>
+      </c>
+      <c r="X55" s="1">
+        <v>1047.4458999999999</v>
+      </c>
+      <c r="Y55" s="1">
+        <v>1475.2036000000001</v>
+      </c>
+      <c r="Z55" s="1">
+        <v>677.12405999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B56">
         <v>0.6</v>
       </c>
@@ -2334,8 +3608,32 @@
       <c r="M56">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S56">
+        <v>1000</v>
+      </c>
+      <c r="T56">
+        <v>1</v>
+      </c>
+      <c r="U56">
+        <v>0.1</v>
+      </c>
+      <c r="V56">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="W56">
+        <v>0.35</v>
+      </c>
+      <c r="X56" s="1">
+        <v>1000.8114</v>
+      </c>
+      <c r="Y56" s="1">
+        <v>1421.7532000000001</v>
+      </c>
+      <c r="Z56" s="1">
+        <v>697.48333000000002</v>
+      </c>
+    </row>
+    <row r="57" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B57">
         <v>0.6</v>
       </c>
@@ -2369,8 +3667,32 @@
       <c r="M57">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S57">
+        <v>1000</v>
+      </c>
+      <c r="T57">
+        <v>1</v>
+      </c>
+      <c r="U57">
+        <v>0.1</v>
+      </c>
+      <c r="V57">
+        <v>0.6</v>
+      </c>
+      <c r="W57">
+        <v>0.3</v>
+      </c>
+      <c r="X57" s="1">
+        <v>948.47775000000001</v>
+      </c>
+      <c r="Y57" s="1">
+        <v>1362.5204000000001</v>
+      </c>
+      <c r="Z57" s="1">
+        <v>716.89730999999995</v>
+      </c>
+    </row>
+    <row r="58" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B58">
         <v>0.6</v>
       </c>
@@ -2404,8 +3726,32 @@
       <c r="M58">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S58">
+        <v>1000</v>
+      </c>
+      <c r="T58">
+        <v>1</v>
+      </c>
+      <c r="U58">
+        <v>0.1</v>
+      </c>
+      <c r="V58">
+        <v>0.65</v>
+      </c>
+      <c r="W58">
+        <v>0.25</v>
+      </c>
+      <c r="X58" s="1">
+        <v>888.27270999999996</v>
+      </c>
+      <c r="Y58" s="1">
+        <v>1295.5092999999999</v>
+      </c>
+      <c r="Z58" s="1">
+        <v>735.74414000000002</v>
+      </c>
+    </row>
+    <row r="59" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B59">
         <v>0.6</v>
       </c>
@@ -2439,8 +3785,32 @@
       <c r="M59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S59">
+        <v>1000</v>
+      </c>
+      <c r="T59">
+        <v>1</v>
+      </c>
+      <c r="U59">
+        <v>0.1</v>
+      </c>
+      <c r="V59">
+        <v>0.7</v>
+      </c>
+      <c r="W59">
+        <v>0.2</v>
+      </c>
+      <c r="X59" s="1">
+        <v>816.73832000000004</v>
+      </c>
+      <c r="Y59" s="1">
+        <v>1217.5878</v>
+      </c>
+      <c r="Z59" s="1">
+        <v>754.36505</v>
+      </c>
+    </row>
+    <row r="60" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B60">
         <v>0.7</v>
       </c>
@@ -2474,8 +3844,32 @@
       <c r="M60">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S60">
+        <v>1000</v>
+      </c>
+      <c r="T60">
+        <v>1</v>
+      </c>
+      <c r="U60">
+        <v>0.1</v>
+      </c>
+      <c r="V60">
+        <v>0.75</v>
+      </c>
+      <c r="W60">
+        <v>0.15</v>
+      </c>
+      <c r="X60" s="1">
+        <v>837.59424999999999</v>
+      </c>
+      <c r="Y60" s="1">
+        <v>1123.2923000000001</v>
+      </c>
+      <c r="Z60" s="1">
+        <v>773.07759999999996</v>
+      </c>
+    </row>
+    <row r="61" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B61">
         <v>0.7</v>
       </c>
@@ -2509,8 +3903,32 @@
       <c r="M61">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S61">
+        <v>1000</v>
+      </c>
+      <c r="T61">
+        <v>1</v>
+      </c>
+      <c r="U61">
+        <v>0.1</v>
+      </c>
+      <c r="V61">
+        <v>0.8</v>
+      </c>
+      <c r="W61">
+        <v>0.1</v>
+      </c>
+      <c r="X61" s="1">
+        <v>844.89652000000001</v>
+      </c>
+      <c r="Y61" s="1">
+        <v>1001.4006000000001</v>
+      </c>
+      <c r="Z61" s="1">
+        <v>792.19056</v>
+      </c>
+    </row>
+    <row r="62" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B62">
         <v>0.7</v>
       </c>
@@ -2544,8 +3962,32 @@
       <c r="M62">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S62">
+        <v>1000</v>
+      </c>
+      <c r="T62">
+        <v>1</v>
+      </c>
+      <c r="U62">
+        <v>0.1</v>
+      </c>
+      <c r="V62">
+        <v>0.85</v>
+      </c>
+      <c r="W62">
+        <v>0.05</v>
+      </c>
+      <c r="X62" s="1">
+        <v>847.76152999999999</v>
+      </c>
+      <c r="Y62" s="1">
+        <v>820.46749</v>
+      </c>
+      <c r="Z62" s="1">
+        <v>812.03195000000005</v>
+      </c>
+    </row>
+    <row r="63" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B63">
         <v>0.7</v>
       </c>
@@ -2579,8 +4021,32 @@
       <c r="M63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S63">
+        <v>1000</v>
+      </c>
+      <c r="T63">
+        <v>1</v>
+      </c>
+      <c r="U63">
+        <v>0.1</v>
+      </c>
+      <c r="V63">
+        <v>0.9</v>
+      </c>
+      <c r="W63">
+        <v>0</v>
+      </c>
+      <c r="X63" s="1">
+        <v>846.25301000000002</v>
+      </c>
+      <c r="Y63" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z63" s="1">
+        <v>833.02697999999998</v>
+      </c>
+    </row>
+    <row r="64" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B64">
         <v>0.8</v>
       </c>
@@ -2614,8 +4080,32 @@
       <c r="M64">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S64">
+        <v>1000</v>
+      </c>
+      <c r="T64">
+        <v>1</v>
+      </c>
+      <c r="U64">
+        <v>0.15</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0.85</v>
+      </c>
+      <c r="X64" s="1">
+        <v>1383.6679999999999</v>
+      </c>
+      <c r="Y64" s="1">
+        <v>1841.6337000000001</v>
+      </c>
+      <c r="Z64" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B65">
         <v>0.8</v>
       </c>
@@ -2649,8 +4139,32 @@
       <c r="M65">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S65">
+        <v>1000</v>
+      </c>
+      <c r="T65">
+        <v>1</v>
+      </c>
+      <c r="U65">
+        <v>0.15</v>
+      </c>
+      <c r="V65">
+        <v>0.05</v>
+      </c>
+      <c r="W65">
+        <v>0.8</v>
+      </c>
+      <c r="X65" s="1">
+        <v>1345.5798</v>
+      </c>
+      <c r="Y65" s="1">
+        <v>1794.2954999999999</v>
+      </c>
+      <c r="Z65" s="1">
+        <v>303.83395000000002</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B66">
         <v>0.8</v>
       </c>
@@ -2684,8 +4198,32 @@
       <c r="M66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S66">
+        <v>1000</v>
+      </c>
+      <c r="T66">
+        <v>1</v>
+      </c>
+      <c r="U66">
+        <v>0.15</v>
+      </c>
+      <c r="V66">
+        <v>0.1</v>
+      </c>
+      <c r="W66">
+        <v>0.75</v>
+      </c>
+      <c r="X66" s="1">
+        <v>1310.9112</v>
+      </c>
+      <c r="Y66" s="1">
+        <v>1750.9484</v>
+      </c>
+      <c r="Z66" s="1">
+        <v>405.57632000000001</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B67">
         <v>0.9</v>
       </c>
@@ -2719,8 +4257,32 @@
       <c r="M67">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S67">
+        <v>1000</v>
+      </c>
+      <c r="T67">
+        <v>1</v>
+      </c>
+      <c r="U67">
+        <v>0.15</v>
+      </c>
+      <c r="V67">
+        <v>0.15</v>
+      </c>
+      <c r="W67">
+        <v>0.7</v>
+      </c>
+      <c r="X67" s="1">
+        <v>1277.7348</v>
+      </c>
+      <c r="Y67" s="1">
+        <v>1709.2101</v>
+      </c>
+      <c r="Z67" s="1">
+        <v>470.42581999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B68">
         <v>0.9</v>
       </c>
@@ -2754,8 +4316,32 @@
       <c r="M68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="S68">
+        <v>1000</v>
+      </c>
+      <c r="T68">
+        <v>1</v>
+      </c>
+      <c r="U68">
+        <v>0.15</v>
+      </c>
+      <c r="V68">
+        <v>0.2</v>
+      </c>
+      <c r="W68">
+        <v>0.65</v>
+      </c>
+      <c r="X68" s="1">
+        <v>1245.0974000000001</v>
+      </c>
+      <c r="Y68" s="1">
+        <v>1667.8875</v>
+      </c>
+      <c r="Z68" s="1">
+        <v>517.82561999999996</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B69">
         <v>1</v>
       </c>
@@ -2788,6 +4374,4320 @@
       </c>
       <c r="M69">
         <v>0</v>
+      </c>
+      <c r="S69">
+        <v>1000</v>
+      </c>
+      <c r="T69">
+        <v>1</v>
+      </c>
+      <c r="U69">
+        <v>0.15</v>
+      </c>
+      <c r="V69">
+        <v>0.25</v>
+      </c>
+      <c r="W69">
+        <v>0.6</v>
+      </c>
+      <c r="X69" s="1">
+        <v>1212.3865000000001</v>
+      </c>
+      <c r="Y69" s="1">
+        <v>1626.1969999999999</v>
+      </c>
+      <c r="Z69" s="1">
+        <v>555.00856999999996</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="S70">
+        <v>1000</v>
+      </c>
+      <c r="T70">
+        <v>1</v>
+      </c>
+      <c r="U70">
+        <v>0.15</v>
+      </c>
+      <c r="V70">
+        <v>0.3</v>
+      </c>
+      <c r="W70">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="X70" s="1">
+        <v>1179.117</v>
+      </c>
+      <c r="Y70" s="1">
+        <v>1583.5075999999999</v>
+      </c>
+      <c r="Z70" s="1">
+        <v>585.52588000000003</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="S71">
+        <v>1000</v>
+      </c>
+      <c r="T71">
+        <v>1</v>
+      </c>
+      <c r="U71">
+        <v>0.15</v>
+      </c>
+      <c r="V71">
+        <v>0.35</v>
+      </c>
+      <c r="W71">
+        <v>0.5</v>
+      </c>
+      <c r="X71" s="1">
+        <v>1144.8349000000001</v>
+      </c>
+      <c r="Y71" s="1">
+        <v>1539.2231999999999</v>
+      </c>
+      <c r="Z71" s="1">
+        <v>611.42094999999995</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="S72">
+        <v>1000</v>
+      </c>
+      <c r="T72">
+        <v>1</v>
+      </c>
+      <c r="U72">
+        <v>0.15</v>
+      </c>
+      <c r="V72">
+        <v>0.4</v>
+      </c>
+      <c r="W72">
+        <v>0.45</v>
+      </c>
+      <c r="X72" s="1">
+        <v>1109.0618999999999</v>
+      </c>
+      <c r="Y72" s="1">
+        <v>1492.7077999999999</v>
+      </c>
+      <c r="Z72" s="1">
+        <v>634.01495999999997</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="S73">
+        <v>1000</v>
+      </c>
+      <c r="T73">
+        <v>1</v>
+      </c>
+      <c r="U73">
+        <v>0.15</v>
+      </c>
+      <c r="V73">
+        <v>0.45</v>
+      </c>
+      <c r="W73">
+        <v>0.4</v>
+      </c>
+      <c r="X73" s="1">
+        <v>1071.2588000000001</v>
+      </c>
+      <c r="Y73" s="1">
+        <v>1443.2147</v>
+      </c>
+      <c r="Z73" s="1">
+        <v>654.24743000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="S74">
+        <v>1000</v>
+      </c>
+      <c r="T74">
+        <v>1</v>
+      </c>
+      <c r="U74">
+        <v>0.15</v>
+      </c>
+      <c r="V74">
+        <v>0.5</v>
+      </c>
+      <c r="W74">
+        <v>0.35</v>
+      </c>
+      <c r="X74" s="1">
+        <v>1030.8386</v>
+      </c>
+      <c r="Y74" s="1">
+        <v>1389.7977000000001</v>
+      </c>
+      <c r="Z74" s="1">
+        <v>672.84094000000005</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="S75">
+        <v>1000</v>
+      </c>
+      <c r="T75">
+        <v>1</v>
+      </c>
+      <c r="U75">
+        <v>0.15</v>
+      </c>
+      <c r="V75">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="W75">
+        <v>0.3</v>
+      </c>
+      <c r="X75" s="1">
+        <v>987.52185999999995</v>
+      </c>
+      <c r="Y75" s="1">
+        <v>1331.172</v>
+      </c>
+      <c r="Z75" s="1">
+        <v>690.38592000000006</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="S76">
+        <v>1000</v>
+      </c>
+      <c r="T76">
+        <v>1</v>
+      </c>
+      <c r="U76">
+        <v>0.15</v>
+      </c>
+      <c r="V76">
+        <v>0.6</v>
+      </c>
+      <c r="W76">
+        <v>0.25</v>
+      </c>
+      <c r="X76" s="1">
+        <v>1055.6112000000001</v>
+      </c>
+      <c r="Y76" s="1">
+        <v>1265.4664</v>
+      </c>
+      <c r="Z76" s="1">
+        <v>707.38549999999998</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="S77">
+        <v>1000</v>
+      </c>
+      <c r="T77">
+        <v>1</v>
+      </c>
+      <c r="U77">
+        <v>0.15</v>
+      </c>
+      <c r="V77">
+        <v>0.65</v>
+      </c>
+      <c r="W77">
+        <v>0.2</v>
+      </c>
+      <c r="X77" s="1">
+        <v>1074.5702000000001</v>
+      </c>
+      <c r="Y77" s="1">
+        <v>1189.7257</v>
+      </c>
+      <c r="Z77" s="1">
+        <v>724.27958999999998</v>
+      </c>
+    </row>
+    <row r="78" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="S78">
+        <v>1000</v>
+      </c>
+      <c r="T78">
+        <v>1</v>
+      </c>
+      <c r="U78">
+        <v>0.15</v>
+      </c>
+      <c r="V78">
+        <v>0.7</v>
+      </c>
+      <c r="W78">
+        <v>0.15</v>
+      </c>
+      <c r="X78" s="1">
+        <v>1091.508</v>
+      </c>
+      <c r="Y78" s="1">
+        <v>1098.7564</v>
+      </c>
+      <c r="Z78" s="1">
+        <v>741.45896000000005</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="S79">
+        <v>1000</v>
+      </c>
+      <c r="T79">
+        <v>1</v>
+      </c>
+      <c r="U79">
+        <v>0.15</v>
+      </c>
+      <c r="V79">
+        <v>0.75</v>
+      </c>
+      <c r="W79">
+        <v>0.1</v>
+      </c>
+      <c r="X79" s="1">
+        <v>1106.732</v>
+      </c>
+      <c r="Y79" s="1">
+        <v>981.82007999999996</v>
+      </c>
+      <c r="Z79" s="1">
+        <v>759.27620000000002</v>
+      </c>
+    </row>
+    <row r="80" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="S80">
+        <v>1000</v>
+      </c>
+      <c r="T80">
+        <v>1</v>
+      </c>
+      <c r="U80">
+        <v>0.15</v>
+      </c>
+      <c r="V80">
+        <v>0.8</v>
+      </c>
+      <c r="W80">
+        <v>0.05</v>
+      </c>
+      <c r="X80" s="1">
+        <v>1120.8608999999999</v>
+      </c>
+      <c r="Y80" s="1">
+        <v>808.65863999999999</v>
+      </c>
+      <c r="Z80" s="1">
+        <v>778.05972999999994</v>
+      </c>
+    </row>
+    <row r="81" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S81">
+        <v>1000</v>
+      </c>
+      <c r="T81">
+        <v>1</v>
+      </c>
+      <c r="U81">
+        <v>0.15</v>
+      </c>
+      <c r="V81">
+        <v>0.85</v>
+      </c>
+      <c r="W81">
+        <v>0</v>
+      </c>
+      <c r="X81" s="1">
+        <v>1135.6320000000001</v>
+      </c>
+      <c r="Y81" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z81" s="1">
+        <v>798.13413000000003</v>
+      </c>
+    </row>
+    <row r="82" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S82">
+        <v>1000</v>
+      </c>
+      <c r="T82">
+        <v>1</v>
+      </c>
+      <c r="U82">
+        <v>0.2</v>
+      </c>
+      <c r="V82">
+        <v>0</v>
+      </c>
+      <c r="W82">
+        <v>0.8</v>
+      </c>
+      <c r="X82" s="1">
+        <v>1367.3891000000001</v>
+      </c>
+      <c r="Y82" s="1">
+        <v>1783.4921999999999</v>
+      </c>
+      <c r="Z82" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S83">
+        <v>1000</v>
+      </c>
+      <c r="T83">
+        <v>1</v>
+      </c>
+      <c r="U83">
+        <v>0.2</v>
+      </c>
+      <c r="V83">
+        <v>0.05</v>
+      </c>
+      <c r="W83">
+        <v>0.75</v>
+      </c>
+      <c r="X83" s="1">
+        <v>1328.9052999999999</v>
+      </c>
+      <c r="Y83" s="1">
+        <v>1731.6722</v>
+      </c>
+      <c r="Z83" s="1">
+        <v>330.73178999999999</v>
+      </c>
+    </row>
+    <row r="84" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S84">
+        <v>1000</v>
+      </c>
+      <c r="T84">
+        <v>1</v>
+      </c>
+      <c r="U84">
+        <v>0.2</v>
+      </c>
+      <c r="V84">
+        <v>0.1</v>
+      </c>
+      <c r="W84">
+        <v>0.7</v>
+      </c>
+      <c r="X84" s="1">
+        <v>1295.2883999999999</v>
+      </c>
+      <c r="Y84" s="1">
+        <v>1684.6475</v>
+      </c>
+      <c r="Z84" s="1">
+        <v>429.30189999999999</v>
+      </c>
+    </row>
+    <row r="85" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S85">
+        <v>1000</v>
+      </c>
+      <c r="T85">
+        <v>1</v>
+      </c>
+      <c r="U85">
+        <v>0.2</v>
+      </c>
+      <c r="V85">
+        <v>0.15</v>
+      </c>
+      <c r="W85">
+        <v>0.65</v>
+      </c>
+      <c r="X85" s="1">
+        <v>1264.3153</v>
+      </c>
+      <c r="Y85" s="1">
+        <v>1639.5479</v>
+      </c>
+      <c r="Z85" s="1">
+        <v>489.61507999999998</v>
+      </c>
+    </row>
+    <row r="86" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S86">
+        <v>1000</v>
+      </c>
+      <c r="T86">
+        <v>1</v>
+      </c>
+      <c r="U86">
+        <v>0.2</v>
+      </c>
+      <c r="V86">
+        <v>0.2</v>
+      </c>
+      <c r="W86">
+        <v>0.6</v>
+      </c>
+      <c r="X86" s="1">
+        <v>1235.1382000000001</v>
+      </c>
+      <c r="Y86" s="1">
+        <v>1594.9874</v>
+      </c>
+      <c r="Z86" s="1">
+        <v>532.22825999999998</v>
+      </c>
+    </row>
+    <row r="87" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S87">
+        <v>1000</v>
+      </c>
+      <c r="T87">
+        <v>1</v>
+      </c>
+      <c r="U87">
+        <v>0.2</v>
+      </c>
+      <c r="V87">
+        <v>0.25</v>
+      </c>
+      <c r="W87">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="X87" s="1">
+        <v>1207.5449000000001</v>
+      </c>
+      <c r="Y87" s="1">
+        <v>1550.0733</v>
+      </c>
+      <c r="Z87" s="1">
+        <v>564.63324999999998</v>
+      </c>
+    </row>
+    <row r="88" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S88">
+        <v>1000</v>
+      </c>
+      <c r="T88">
+        <v>1</v>
+      </c>
+      <c r="U88">
+        <v>0.2</v>
+      </c>
+      <c r="V88">
+        <v>0.3</v>
+      </c>
+      <c r="W88">
+        <v>0.5</v>
+      </c>
+      <c r="X88" s="1">
+        <v>1181.97</v>
+      </c>
+      <c r="Y88" s="1">
+        <v>1504.0913</v>
+      </c>
+      <c r="Z88" s="1">
+        <v>590.48329000000001</v>
+      </c>
+    </row>
+    <row r="89" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S89">
+        <v>1000</v>
+      </c>
+      <c r="T89">
+        <v>1</v>
+      </c>
+      <c r="U89">
+        <v>0.2</v>
+      </c>
+      <c r="V89">
+        <v>0.35</v>
+      </c>
+      <c r="W89">
+        <v>0.45</v>
+      </c>
+      <c r="X89" s="1">
+        <v>1160.6168</v>
+      </c>
+      <c r="Y89" s="1">
+        <v>1456.3598</v>
+      </c>
+      <c r="Z89" s="1">
+        <v>611.89523999999994</v>
+      </c>
+    </row>
+    <row r="90" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S90">
+        <v>1000</v>
+      </c>
+      <c r="T90">
+        <v>1</v>
+      </c>
+      <c r="U90">
+        <v>0.2</v>
+      </c>
+      <c r="V90">
+        <v>0.4</v>
+      </c>
+      <c r="W90">
+        <v>0.4</v>
+      </c>
+      <c r="X90" s="1">
+        <v>1191.3163</v>
+      </c>
+      <c r="Y90" s="1">
+        <v>1406.1305</v>
+      </c>
+      <c r="Z90" s="1">
+        <v>630.26334999999995</v>
+      </c>
+    </row>
+    <row r="91" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S91">
+        <v>1000</v>
+      </c>
+      <c r="T91">
+        <v>1</v>
+      </c>
+      <c r="U91">
+        <v>0.2</v>
+      </c>
+      <c r="V91">
+        <v>0.45</v>
+      </c>
+      <c r="W91">
+        <v>0.35</v>
+      </c>
+      <c r="X91" s="1">
+        <v>1218.7584999999999</v>
+      </c>
+      <c r="Y91" s="1">
+        <v>1352.4866999999999</v>
+      </c>
+      <c r="Z91" s="1">
+        <v>646.60334</v>
+      </c>
+    </row>
+    <row r="92" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S92">
+        <v>1000</v>
+      </c>
+      <c r="T92">
+        <v>1</v>
+      </c>
+      <c r="U92">
+        <v>0.2</v>
+      </c>
+      <c r="V92">
+        <v>0.5</v>
+      </c>
+      <c r="W92">
+        <v>0.3</v>
+      </c>
+      <c r="X92" s="1">
+        <v>1244.3956000000001</v>
+      </c>
+      <c r="Y92" s="1">
+        <v>1294.2002</v>
+      </c>
+      <c r="Z92" s="1">
+        <v>661.71307999999999</v>
+      </c>
+    </row>
+    <row r="93" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S93">
+        <v>1000</v>
+      </c>
+      <c r="T93">
+        <v>1</v>
+      </c>
+      <c r="U93">
+        <v>0.2</v>
+      </c>
+      <c r="V93">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="W93">
+        <v>0.25</v>
+      </c>
+      <c r="X93" s="1">
+        <v>1268.5</v>
+      </c>
+      <c r="Y93" s="1">
+        <v>1229.4873</v>
+      </c>
+      <c r="Z93" s="1">
+        <v>676.25084000000004</v>
+      </c>
+    </row>
+    <row r="94" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S94">
+        <v>1000</v>
+      </c>
+      <c r="T94">
+        <v>1</v>
+      </c>
+      <c r="U94">
+        <v>0.2</v>
+      </c>
+      <c r="V94">
+        <v>0.6</v>
+      </c>
+      <c r="W94">
+        <v>0.2</v>
+      </c>
+      <c r="X94" s="1">
+        <v>1291.4104</v>
+      </c>
+      <c r="Y94" s="1">
+        <v>1155.5266999999999</v>
+      </c>
+      <c r="Z94" s="1">
+        <v>690.77319</v>
+      </c>
+    </row>
+    <row r="95" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S95">
+        <v>1000</v>
+      </c>
+      <c r="T95">
+        <v>1</v>
+      </c>
+      <c r="U95">
+        <v>0.2</v>
+      </c>
+      <c r="V95">
+        <v>0.65</v>
+      </c>
+      <c r="W95">
+        <v>0.15</v>
+      </c>
+      <c r="X95" s="1">
+        <v>1313.5618999999999</v>
+      </c>
+      <c r="Y95" s="1">
+        <v>1067.3520000000001</v>
+      </c>
+      <c r="Z95" s="1">
+        <v>705.75252999999998</v>
+      </c>
+    </row>
+    <row r="96" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S96">
+        <v>1000</v>
+      </c>
+      <c r="T96">
+        <v>1</v>
+      </c>
+      <c r="U96">
+        <v>0.2</v>
+      </c>
+      <c r="V96">
+        <v>0.7</v>
+      </c>
+      <c r="W96">
+        <v>0.1</v>
+      </c>
+      <c r="X96" s="1">
+        <v>1335.5779</v>
+      </c>
+      <c r="Y96" s="1">
+        <v>954.68624</v>
+      </c>
+      <c r="Z96" s="1">
+        <v>721.58447000000001</v>
+      </c>
+    </row>
+    <row r="97" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S97">
+        <v>1000</v>
+      </c>
+      <c r="T97">
+        <v>1</v>
+      </c>
+      <c r="U97">
+        <v>0.2</v>
+      </c>
+      <c r="V97">
+        <v>0.75</v>
+      </c>
+      <c r="W97">
+        <v>0.05</v>
+      </c>
+      <c r="X97" s="1">
+        <v>1358.4835</v>
+      </c>
+      <c r="Y97" s="1">
+        <v>788.55918999999994</v>
+      </c>
+      <c r="Z97" s="1">
+        <v>738.58873000000006</v>
+      </c>
+    </row>
+    <row r="98" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S98">
+        <v>1000</v>
+      </c>
+      <c r="T98">
+        <v>1</v>
+      </c>
+      <c r="U98">
+        <v>0.2</v>
+      </c>
+      <c r="V98">
+        <v>0.8</v>
+      </c>
+      <c r="W98">
+        <v>0</v>
+      </c>
+      <c r="X98" s="1">
+        <v>1384.3040000000001</v>
+      </c>
+      <c r="Y98" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z98" s="1">
+        <v>756.99441000000002</v>
+      </c>
+    </row>
+    <row r="99" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S99">
+        <v>1000</v>
+      </c>
+      <c r="T99">
+        <v>1</v>
+      </c>
+      <c r="U99">
+        <v>0.25</v>
+      </c>
+      <c r="V99">
+        <v>0</v>
+      </c>
+      <c r="W99">
+        <v>0.75</v>
+      </c>
+      <c r="X99" s="1">
+        <v>1359.3871999999999</v>
+      </c>
+      <c r="Y99" s="1">
+        <v>1716.4321</v>
+      </c>
+      <c r="Z99" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S100">
+        <v>1000</v>
+      </c>
+      <c r="T100">
+        <v>1</v>
+      </c>
+      <c r="U100">
+        <v>0.25</v>
+      </c>
+      <c r="V100">
+        <v>0.05</v>
+      </c>
+      <c r="W100">
+        <v>0.7</v>
+      </c>
+      <c r="X100" s="1">
+        <v>1325.4963</v>
+      </c>
+      <c r="Y100" s="1">
+        <v>1659.8806</v>
+      </c>
+      <c r="Z100" s="1">
+        <v>358.33091999999999</v>
+      </c>
+    </row>
+    <row r="101" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S101">
+        <v>1000</v>
+      </c>
+      <c r="T101">
+        <v>1</v>
+      </c>
+      <c r="U101">
+        <v>0.25</v>
+      </c>
+      <c r="V101">
+        <v>0.1</v>
+      </c>
+      <c r="W101">
+        <v>0.65</v>
+      </c>
+      <c r="X101" s="1">
+        <v>1300.1739</v>
+      </c>
+      <c r="Y101" s="1">
+        <v>1608.9402</v>
+      </c>
+      <c r="Z101" s="1">
+        <v>451.41764000000001</v>
+      </c>
+    </row>
+    <row r="102" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S102">
+        <v>1000</v>
+      </c>
+      <c r="T102">
+        <v>1</v>
+      </c>
+      <c r="U102">
+        <v>0.25</v>
+      </c>
+      <c r="V102">
+        <v>0.15</v>
+      </c>
+      <c r="W102">
+        <v>0.6</v>
+      </c>
+      <c r="X102" s="1">
+        <v>1282.7107000000001</v>
+      </c>
+      <c r="Y102" s="1">
+        <v>1560.2266</v>
+      </c>
+      <c r="Z102" s="1">
+        <v>505.60338999999999</v>
+      </c>
+    </row>
+    <row r="103" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S103">
+        <v>1000</v>
+      </c>
+      <c r="T103">
+        <v>1</v>
+      </c>
+      <c r="U103">
+        <v>0.25</v>
+      </c>
+      <c r="V103">
+        <v>0.2</v>
+      </c>
+      <c r="W103">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="X103" s="1">
+        <v>1278.5505000000001</v>
+      </c>
+      <c r="Y103" s="1">
+        <v>1512.1677</v>
+      </c>
+      <c r="Z103" s="1">
+        <v>542.18098999999995</v>
+      </c>
+    </row>
+    <row r="104" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S104">
+        <v>1000</v>
+      </c>
+      <c r="T104">
+        <v>1</v>
+      </c>
+      <c r="U104">
+        <v>0.25</v>
+      </c>
+      <c r="V104">
+        <v>0.25</v>
+      </c>
+      <c r="W104">
+        <v>0.5</v>
+      </c>
+      <c r="X104" s="1">
+        <v>1311.3300999999999</v>
+      </c>
+      <c r="Y104" s="1">
+        <v>1463.7611999999999</v>
+      </c>
+      <c r="Z104" s="1">
+        <v>568.74928999999997</v>
+      </c>
+    </row>
+    <row r="105" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S105">
+        <v>1000</v>
+      </c>
+      <c r="T105">
+        <v>1</v>
+      </c>
+      <c r="U105">
+        <v>0.25</v>
+      </c>
+      <c r="V105">
+        <v>0.3</v>
+      </c>
+      <c r="W105">
+        <v>0.45</v>
+      </c>
+      <c r="X105" s="1">
+        <v>1344.4342999999999</v>
+      </c>
+      <c r="Y105" s="1">
+        <v>1414.1972000000001</v>
+      </c>
+      <c r="Z105" s="1">
+        <v>589.01323000000002</v>
+      </c>
+    </row>
+    <row r="106" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S106">
+        <v>1000</v>
+      </c>
+      <c r="T106">
+        <v>1</v>
+      </c>
+      <c r="U106">
+        <v>0.25</v>
+      </c>
+      <c r="V106">
+        <v>0.35</v>
+      </c>
+      <c r="W106">
+        <v>0.4</v>
+      </c>
+      <c r="X106" s="1">
+        <v>1375.6867</v>
+      </c>
+      <c r="Y106" s="1">
+        <v>1362.6794</v>
+      </c>
+      <c r="Z106" s="1">
+        <v>605.15367000000003</v>
+      </c>
+    </row>
+    <row r="107" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S107">
+        <v>1000</v>
+      </c>
+      <c r="T107">
+        <v>1</v>
+      </c>
+      <c r="U107">
+        <v>0.25</v>
+      </c>
+      <c r="V107">
+        <v>0.4</v>
+      </c>
+      <c r="W107">
+        <v>0.35</v>
+      </c>
+      <c r="X107" s="1">
+        <v>1405.2373</v>
+      </c>
+      <c r="Y107" s="1">
+        <v>1308.2927999999999</v>
+      </c>
+      <c r="Z107" s="1">
+        <v>618.64421000000004</v>
+      </c>
+    </row>
+    <row r="108" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S108">
+        <v>1000</v>
+      </c>
+      <c r="T108">
+        <v>1</v>
+      </c>
+      <c r="U108">
+        <v>0.25</v>
+      </c>
+      <c r="V108">
+        <v>0.45</v>
+      </c>
+      <c r="W108">
+        <v>0.3</v>
+      </c>
+      <c r="X108" s="1">
+        <v>1433.4158</v>
+      </c>
+      <c r="Y108" s="1">
+        <v>1249.8487</v>
+      </c>
+      <c r="Z108" s="1">
+        <v>630.58632999999998</v>
+      </c>
+    </row>
+    <row r="109" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S109">
+        <v>1000</v>
+      </c>
+      <c r="T109">
+        <v>1</v>
+      </c>
+      <c r="U109">
+        <v>0.25</v>
+      </c>
+      <c r="V109">
+        <v>0.5</v>
+      </c>
+      <c r="W109">
+        <v>0.25</v>
+      </c>
+      <c r="X109" s="1">
+        <v>1460.6103000000001</v>
+      </c>
+      <c r="Y109" s="1">
+        <v>1185.6433999999999</v>
+      </c>
+      <c r="Z109" s="1">
+        <v>641.85798999999997</v>
+      </c>
+    </row>
+    <row r="110" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S110">
+        <v>1000</v>
+      </c>
+      <c r="T110">
+        <v>1</v>
+      </c>
+      <c r="U110">
+        <v>0.25</v>
+      </c>
+      <c r="V110">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="W110">
+        <v>0.2</v>
+      </c>
+      <c r="X110" s="1">
+        <v>1487.2648999999999</v>
+      </c>
+      <c r="Y110" s="1">
+        <v>1112.9951000000001</v>
+      </c>
+      <c r="Z110" s="1">
+        <v>653.17912000000001</v>
+      </c>
+    </row>
+    <row r="111" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S111">
+        <v>1000</v>
+      </c>
+      <c r="T111">
+        <v>1</v>
+      </c>
+      <c r="U111">
+        <v>0.25</v>
+      </c>
+      <c r="V111">
+        <v>0.6</v>
+      </c>
+      <c r="W111">
+        <v>0.15</v>
+      </c>
+      <c r="X111" s="1">
+        <v>1513.9161999999999</v>
+      </c>
+      <c r="Y111" s="1">
+        <v>1027.1922</v>
+      </c>
+      <c r="Z111" s="1">
+        <v>665.13787000000002</v>
+      </c>
+    </row>
+    <row r="112" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S112">
+        <v>1000</v>
+      </c>
+      <c r="T112">
+        <v>1</v>
+      </c>
+      <c r="U112">
+        <v>0.25</v>
+      </c>
+      <c r="V112">
+        <v>0.65</v>
+      </c>
+      <c r="W112">
+        <v>0.1</v>
+      </c>
+      <c r="X112" s="1">
+        <v>1541.2671</v>
+      </c>
+      <c r="Y112" s="1">
+        <v>918.49557000000004</v>
+      </c>
+      <c r="Z112" s="1">
+        <v>678.19820000000004</v>
+      </c>
+    </row>
+    <row r="113" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S113">
+        <v>1000</v>
+      </c>
+      <c r="T113">
+        <v>1</v>
+      </c>
+      <c r="U113">
+        <v>0.25</v>
+      </c>
+      <c r="V113">
+        <v>0.7</v>
+      </c>
+      <c r="W113">
+        <v>0.05</v>
+      </c>
+      <c r="X113" s="1">
+        <v>1570.3267000000001</v>
+      </c>
+      <c r="Y113" s="1">
+        <v>759.44223999999997</v>
+      </c>
+      <c r="Z113" s="1">
+        <v>692.69704999999999</v>
+      </c>
+    </row>
+    <row r="114" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S114">
+        <v>1000</v>
+      </c>
+      <c r="T114">
+        <v>1</v>
+      </c>
+      <c r="U114">
+        <v>0.25</v>
+      </c>
+      <c r="V114">
+        <v>0.75</v>
+      </c>
+      <c r="W114">
+        <v>0</v>
+      </c>
+      <c r="X114" s="1">
+        <v>1602.7535</v>
+      </c>
+      <c r="Y114" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z114" s="1">
+        <v>708.82677000000001</v>
+      </c>
+    </row>
+    <row r="115" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S115">
+        <v>1000</v>
+      </c>
+      <c r="T115">
+        <v>1</v>
+      </c>
+      <c r="U115">
+        <v>0.3</v>
+      </c>
+      <c r="V115">
+        <v>0</v>
+      </c>
+      <c r="W115">
+        <v>0.7</v>
+      </c>
+      <c r="X115" s="1">
+        <v>1380.2361000000001</v>
+      </c>
+      <c r="Y115" s="1">
+        <v>1638.2657999999999</v>
+      </c>
+      <c r="Z115" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S116">
+        <v>1000</v>
+      </c>
+      <c r="T116">
+        <v>1</v>
+      </c>
+      <c r="U116">
+        <v>0.3</v>
+      </c>
+      <c r="V116">
+        <v>0.05</v>
+      </c>
+      <c r="W116">
+        <v>0.65</v>
+      </c>
+      <c r="X116" s="1">
+        <v>1373.452</v>
+      </c>
+      <c r="Y116" s="1">
+        <v>1576.7983999999999</v>
+      </c>
+      <c r="Z116" s="1">
+        <v>385.26618000000002</v>
+      </c>
+    </row>
+    <row r="117" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S117">
+        <v>1000</v>
+      </c>
+      <c r="T117">
+        <v>1</v>
+      </c>
+      <c r="U117">
+        <v>0.3</v>
+      </c>
+      <c r="V117">
+        <v>0.1</v>
+      </c>
+      <c r="W117">
+        <v>0.6</v>
+      </c>
+      <c r="X117" s="1">
+        <v>1400.5224000000001</v>
+      </c>
+      <c r="Y117" s="1">
+        <v>1521.6522</v>
+      </c>
+      <c r="Z117" s="1">
+        <v>470.09507000000002</v>
+      </c>
+    </row>
+    <row r="118" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S118">
+        <v>1000</v>
+      </c>
+      <c r="T118">
+        <v>1</v>
+      </c>
+      <c r="U118">
+        <v>0.3</v>
+      </c>
+      <c r="V118">
+        <v>0.15</v>
+      </c>
+      <c r="W118">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="X118" s="1">
+        <v>1439.6642999999999</v>
+      </c>
+      <c r="Y118" s="1">
+        <v>1468.9547</v>
+      </c>
+      <c r="Z118" s="1">
+        <v>516.33016999999995</v>
+      </c>
+    </row>
+    <row r="119" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S119">
+        <v>1000</v>
+      </c>
+      <c r="T119">
+        <v>1</v>
+      </c>
+      <c r="U119">
+        <v>0.3</v>
+      </c>
+      <c r="V119">
+        <v>0.2</v>
+      </c>
+      <c r="W119">
+        <v>0.5</v>
+      </c>
+      <c r="X119" s="1">
+        <v>1477.0767000000001</v>
+      </c>
+      <c r="Y119" s="1">
+        <v>1416.9706000000001</v>
+      </c>
+      <c r="Z119" s="1">
+        <v>545.39007000000004</v>
+      </c>
+    </row>
+    <row r="120" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S120">
+        <v>1000</v>
+      </c>
+      <c r="T120">
+        <v>1</v>
+      </c>
+      <c r="U120">
+        <v>0.3</v>
+      </c>
+      <c r="V120">
+        <v>0.25</v>
+      </c>
+      <c r="W120">
+        <v>0.45</v>
+      </c>
+      <c r="X120" s="1">
+        <v>1512.1478</v>
+      </c>
+      <c r="Y120" s="1">
+        <v>1364.5949000000001</v>
+      </c>
+      <c r="Z120" s="1">
+        <v>564.80389000000002</v>
+      </c>
+    </row>
+    <row r="121" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S121">
+        <v>1000</v>
+      </c>
+      <c r="T121">
+        <v>1</v>
+      </c>
+      <c r="U121">
+        <v>0.3</v>
+      </c>
+      <c r="V121">
+        <v>0.3</v>
+      </c>
+      <c r="W121">
+        <v>0.4</v>
+      </c>
+      <c r="X121" s="1">
+        <v>1545.1866</v>
+      </c>
+      <c r="Y121" s="1">
+        <v>1310.9141</v>
+      </c>
+      <c r="Z121" s="1">
+        <v>578.29268999999999</v>
+      </c>
+    </row>
+    <row r="122" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S122">
+        <v>1000</v>
+      </c>
+      <c r="T122">
+        <v>1</v>
+      </c>
+      <c r="U122">
+        <v>0.3</v>
+      </c>
+      <c r="V122">
+        <v>0.35</v>
+      </c>
+      <c r="W122">
+        <v>0.35</v>
+      </c>
+      <c r="X122" s="1">
+        <v>1576.6267</v>
+      </c>
+      <c r="Y122" s="1">
+        <v>1254.9908</v>
+      </c>
+      <c r="Z122" s="1">
+        <v>588.12363000000005</v>
+      </c>
+    </row>
+    <row r="123" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S123">
+        <v>1000</v>
+      </c>
+      <c r="T123">
+        <v>1</v>
+      </c>
+      <c r="U123">
+        <v>0.3</v>
+      </c>
+      <c r="V123">
+        <v>0.4</v>
+      </c>
+      <c r="W123">
+        <v>0.3</v>
+      </c>
+      <c r="X123" s="1">
+        <v>1606.9154000000001</v>
+      </c>
+      <c r="Y123" s="1">
+        <v>1195.6818000000001</v>
+      </c>
+      <c r="Z123" s="1">
+        <v>595.89418000000001</v>
+      </c>
+    </row>
+    <row r="124" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S124">
+        <v>1000</v>
+      </c>
+      <c r="T124">
+        <v>1</v>
+      </c>
+      <c r="U124">
+        <v>0.3</v>
+      </c>
+      <c r="V124">
+        <v>0.45</v>
+      </c>
+      <c r="W124">
+        <v>0.25</v>
+      </c>
+      <c r="X124" s="1">
+        <v>1636.5047999999999</v>
+      </c>
+      <c r="Y124" s="1">
+        <v>1131.3939</v>
+      </c>
+      <c r="Z124" s="1">
+        <v>602.83376999999996</v>
+      </c>
+    </row>
+    <row r="125" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S125">
+        <v>1000</v>
+      </c>
+      <c r="T125">
+        <v>1</v>
+      </c>
+      <c r="U125">
+        <v>0.3</v>
+      </c>
+      <c r="V125">
+        <v>0.5</v>
+      </c>
+      <c r="W125">
+        <v>0.2</v>
+      </c>
+      <c r="X125" s="1">
+        <v>1665.8690999999999</v>
+      </c>
+      <c r="Y125" s="1">
+        <v>1059.6413</v>
+      </c>
+      <c r="Z125" s="1">
+        <v>609.92151000000001</v>
+      </c>
+    </row>
+    <row r="126" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S126">
+        <v>1000</v>
+      </c>
+      <c r="T126">
+        <v>1</v>
+      </c>
+      <c r="U126">
+        <v>0.3</v>
+      </c>
+      <c r="V126">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="W126">
+        <v>0.15</v>
+      </c>
+      <c r="X126" s="1">
+        <v>1695.5353</v>
+      </c>
+      <c r="Y126" s="1">
+        <v>976.05588999999998</v>
+      </c>
+      <c r="Z126" s="1">
+        <v>617.92853000000002</v>
+      </c>
+    </row>
+    <row r="127" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S127">
+        <v>1000</v>
+      </c>
+      <c r="T127">
+        <v>1</v>
+      </c>
+      <c r="U127">
+        <v>0.3</v>
+      </c>
+      <c r="V127">
+        <v>0.6</v>
+      </c>
+      <c r="W127">
+        <v>0.1</v>
+      </c>
+      <c r="X127" s="1">
+        <v>1726.1305</v>
+      </c>
+      <c r="Y127" s="1">
+        <v>871.57485999999994</v>
+      </c>
+      <c r="Z127" s="1">
+        <v>627.43251999999995</v>
+      </c>
+    </row>
+    <row r="128" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S128">
+        <v>1000</v>
+      </c>
+      <c r="T128">
+        <v>1</v>
+      </c>
+      <c r="U128">
+        <v>0.3</v>
+      </c>
+      <c r="V128">
+        <v>0.65</v>
+      </c>
+      <c r="W128">
+        <v>0.05</v>
+      </c>
+      <c r="X128" s="1">
+        <v>1758.4611</v>
+      </c>
+      <c r="Y128" s="1">
+        <v>720.50019999999995</v>
+      </c>
+      <c r="Z128" s="1">
+        <v>638.82449999999994</v>
+      </c>
+    </row>
+    <row r="129" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S129">
+        <v>1000</v>
+      </c>
+      <c r="T129">
+        <v>1</v>
+      </c>
+      <c r="U129">
+        <v>0.3</v>
+      </c>
+      <c r="V129">
+        <v>0.7</v>
+      </c>
+      <c r="W129">
+        <v>0</v>
+      </c>
+      <c r="X129" s="1">
+        <v>1793.6532999999999</v>
+      </c>
+      <c r="Y129" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z129" s="1">
+        <v>652.31083999999998</v>
+      </c>
+    </row>
+    <row r="130" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S130">
+        <v>1000</v>
+      </c>
+      <c r="T130">
+        <v>1</v>
+      </c>
+      <c r="U130">
+        <v>0.35</v>
+      </c>
+      <c r="V130">
+        <v>0</v>
+      </c>
+      <c r="W130">
+        <v>0.65</v>
+      </c>
+      <c r="X130" s="1">
+        <v>1511.5346</v>
+      </c>
+      <c r="Y130" s="1">
+        <v>1545.4384</v>
+      </c>
+      <c r="Z130" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S131">
+        <v>1000</v>
+      </c>
+      <c r="T131">
+        <v>1</v>
+      </c>
+      <c r="U131">
+        <v>0.35</v>
+      </c>
+      <c r="V131">
+        <v>0.05</v>
+      </c>
+      <c r="W131">
+        <v>0.6</v>
+      </c>
+      <c r="X131" s="1">
+        <v>1554.7761</v>
+      </c>
+      <c r="Y131" s="1">
+        <v>1478.8667</v>
+      </c>
+      <c r="Z131" s="1">
+        <v>409.40940000000001</v>
+      </c>
+    </row>
+    <row r="132" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S132">
+        <v>1000</v>
+      </c>
+      <c r="T132">
+        <v>1</v>
+      </c>
+      <c r="U132">
+        <v>0.35</v>
+      </c>
+      <c r="V132">
+        <v>0.1</v>
+      </c>
+      <c r="W132">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="X132" s="1">
+        <v>1595.7537</v>
+      </c>
+      <c r="Y132" s="1">
+        <v>1418.9924000000001</v>
+      </c>
+      <c r="Z132" s="1">
+        <v>482.61745000000002</v>
+      </c>
+    </row>
+    <row r="133" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S133">
+        <v>1000</v>
+      </c>
+      <c r="T133">
+        <v>1</v>
+      </c>
+      <c r="U133">
+        <v>0.35</v>
+      </c>
+      <c r="V133">
+        <v>0.15</v>
+      </c>
+      <c r="W133">
+        <v>0.5</v>
+      </c>
+      <c r="X133" s="1">
+        <v>1633.8050000000001</v>
+      </c>
+      <c r="Y133" s="1">
+        <v>1361.6137000000001</v>
+      </c>
+      <c r="Z133" s="1">
+        <v>518.46420000000001</v>
+      </c>
+    </row>
+    <row r="134" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S134">
+        <v>1000</v>
+      </c>
+      <c r="T134">
+        <v>1</v>
+      </c>
+      <c r="U134">
+        <v>0.35</v>
+      </c>
+      <c r="V134">
+        <v>0.2</v>
+      </c>
+      <c r="W134">
+        <v>0.45</v>
+      </c>
+      <c r="X134" s="1">
+        <v>1669.365</v>
+      </c>
+      <c r="Y134" s="1">
+        <v>1304.9104</v>
+      </c>
+      <c r="Z134" s="1">
+        <v>537.78851999999995</v>
+      </c>
+    </row>
+    <row r="135" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S135">
+        <v>1000</v>
+      </c>
+      <c r="T135">
+        <v>1</v>
+      </c>
+      <c r="U135">
+        <v>0.35</v>
+      </c>
+      <c r="V135">
+        <v>0.25</v>
+      </c>
+      <c r="W135">
+        <v>0.4</v>
+      </c>
+      <c r="X135" s="1">
+        <v>1702.9604999999999</v>
+      </c>
+      <c r="Y135" s="1">
+        <v>1247.7285999999999</v>
+      </c>
+      <c r="Z135" s="1">
+        <v>547.96992999999998</v>
+      </c>
+    </row>
+    <row r="136" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S136">
+        <v>1000</v>
+      </c>
+      <c r="T136">
+        <v>1</v>
+      </c>
+      <c r="U136">
+        <v>0.35</v>
+      </c>
+      <c r="V136">
+        <v>0.3</v>
+      </c>
+      <c r="W136">
+        <v>0.35</v>
+      </c>
+      <c r="X136" s="1">
+        <v>1735.0933</v>
+      </c>
+      <c r="Y136" s="1">
+        <v>1189.0983000000001</v>
+      </c>
+      <c r="Z136" s="1">
+        <v>552.85154</v>
+      </c>
+    </row>
+    <row r="137" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S137">
+        <v>1000</v>
+      </c>
+      <c r="T137">
+        <v>1</v>
+      </c>
+      <c r="U137">
+        <v>0.35</v>
+      </c>
+      <c r="V137">
+        <v>0.35</v>
+      </c>
+      <c r="W137">
+        <v>0.3</v>
+      </c>
+      <c r="X137" s="1">
+        <v>1766.23</v>
+      </c>
+      <c r="Y137" s="1">
+        <v>1127.9727</v>
+      </c>
+      <c r="Z137" s="1">
+        <v>554.94906000000003</v>
+      </c>
+    </row>
+    <row r="138" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S138">
+        <v>1000</v>
+      </c>
+      <c r="T138">
+        <v>1</v>
+      </c>
+      <c r="U138">
+        <v>0.35</v>
+      </c>
+      <c r="V138">
+        <v>0.4</v>
+      </c>
+      <c r="W138">
+        <v>0.25</v>
+      </c>
+      <c r="X138" s="1">
+        <v>1796.8145999999999</v>
+      </c>
+      <c r="Y138" s="1">
+        <v>1062.9616000000001</v>
+      </c>
+      <c r="Z138" s="1">
+        <v>556.11654999999996</v>
+      </c>
+    </row>
+    <row r="139" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S139">
+        <v>1000</v>
+      </c>
+      <c r="T139">
+        <v>1</v>
+      </c>
+      <c r="U139">
+        <v>0.35</v>
+      </c>
+      <c r="V139">
+        <v>0.45</v>
+      </c>
+      <c r="W139">
+        <v>0.2</v>
+      </c>
+      <c r="X139" s="1">
+        <v>1827.2863</v>
+      </c>
+      <c r="Y139" s="1">
+        <v>991.89318000000003</v>
+      </c>
+      <c r="Z139" s="1">
+        <v>557.75837000000001</v>
+      </c>
+    </row>
+    <row r="140" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S140">
+        <v>1000</v>
+      </c>
+      <c r="T140">
+        <v>1</v>
+      </c>
+      <c r="U140">
+        <v>0.35</v>
+      </c>
+      <c r="V140">
+        <v>0.5</v>
+      </c>
+      <c r="W140">
+        <v>0.15</v>
+      </c>
+      <c r="X140" s="1">
+        <v>1858.1016999999999</v>
+      </c>
+      <c r="Y140" s="1">
+        <v>910.86656000000005</v>
+      </c>
+      <c r="Z140" s="1">
+        <v>560.90351999999996</v>
+      </c>
+    </row>
+    <row r="141" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S141">
+        <v>1000</v>
+      </c>
+      <c r="T141">
+        <v>1</v>
+      </c>
+      <c r="U141">
+        <v>0.35</v>
+      </c>
+      <c r="V141">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="W141">
+        <v>0.1</v>
+      </c>
+      <c r="X141" s="1">
+        <v>1889.7645</v>
+      </c>
+      <c r="Y141" s="1">
+        <v>811.61514999999997</v>
+      </c>
+      <c r="Z141" s="1">
+        <v>566.25242000000003</v>
+      </c>
+    </row>
+    <row r="142" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S142">
+        <v>1000</v>
+      </c>
+      <c r="T142">
+        <v>1</v>
+      </c>
+      <c r="U142">
+        <v>0.35</v>
+      </c>
+      <c r="V142">
+        <v>0.6</v>
+      </c>
+      <c r="W142">
+        <v>0.05</v>
+      </c>
+      <c r="X142" s="1">
+        <v>1922.8679</v>
+      </c>
+      <c r="Y142" s="1">
+        <v>670.39135999999996</v>
+      </c>
+      <c r="Z142" s="1">
+        <v>574.22553000000005</v>
+      </c>
+    </row>
+    <row r="143" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S143">
+        <v>1000</v>
+      </c>
+      <c r="T143">
+        <v>1</v>
+      </c>
+      <c r="U143">
+        <v>0.35</v>
+      </c>
+      <c r="V143">
+        <v>0.65</v>
+      </c>
+      <c r="W143">
+        <v>0</v>
+      </c>
+      <c r="X143" s="1">
+        <v>1958.088</v>
+      </c>
+      <c r="Y143" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z143" s="1">
+        <v>585.01085</v>
+      </c>
+    </row>
+    <row r="144" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S144">
+        <v>1000</v>
+      </c>
+      <c r="T144">
+        <v>1</v>
+      </c>
+      <c r="U144">
+        <v>0.4</v>
+      </c>
+      <c r="V144">
+        <v>0</v>
+      </c>
+      <c r="W144">
+        <v>0.6</v>
+      </c>
+      <c r="X144" s="1">
+        <v>1714.0610999999999</v>
+      </c>
+      <c r="Y144" s="1">
+        <v>1431.6179999999999</v>
+      </c>
+      <c r="Z144" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S145">
+        <v>1000</v>
+      </c>
+      <c r="T145">
+        <v>1</v>
+      </c>
+      <c r="U145">
+        <v>0.4</v>
+      </c>
+      <c r="V145">
+        <v>0.05</v>
+      </c>
+      <c r="W145">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="X145" s="1">
+        <v>1749.4884999999999</v>
+      </c>
+      <c r="Y145" s="1">
+        <v>1359.5603000000001</v>
+      </c>
+      <c r="Z145" s="1">
+        <v>426.80390999999997</v>
+      </c>
+    </row>
+    <row r="146" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S146">
+        <v>1000</v>
+      </c>
+      <c r="T146">
+        <v>1</v>
+      </c>
+      <c r="U146">
+        <v>0.4</v>
+      </c>
+      <c r="V146">
+        <v>0.1</v>
+      </c>
+      <c r="W146">
+        <v>0.5</v>
+      </c>
+      <c r="X146" s="1">
+        <v>1784.2920999999999</v>
+      </c>
+      <c r="Y146" s="1">
+        <v>1293.8457000000001</v>
+      </c>
+      <c r="Z146" s="1">
+        <v>483.38024999999999</v>
+      </c>
+    </row>
+    <row r="147" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S147">
+        <v>1000</v>
+      </c>
+      <c r="T147">
+        <v>1</v>
+      </c>
+      <c r="U147">
+        <v>0.4</v>
+      </c>
+      <c r="V147">
+        <v>0.15</v>
+      </c>
+      <c r="W147">
+        <v>0.45</v>
+      </c>
+      <c r="X147" s="1">
+        <v>1817.6533999999999</v>
+      </c>
+      <c r="Y147" s="1">
+        <v>1230.4222</v>
+      </c>
+      <c r="Z147" s="1">
+        <v>504.41779000000002</v>
+      </c>
+    </row>
+    <row r="148" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S148">
+        <v>1000</v>
+      </c>
+      <c r="T148">
+        <v>1</v>
+      </c>
+      <c r="U148">
+        <v>0.4</v>
+      </c>
+      <c r="V148">
+        <v>0.2</v>
+      </c>
+      <c r="W148">
+        <v>0.4</v>
+      </c>
+      <c r="X148" s="1">
+        <v>1849.6832999999999</v>
+      </c>
+      <c r="Y148" s="1">
+        <v>1167.6409000000001</v>
+      </c>
+      <c r="Z148" s="1">
+        <v>509.83251000000001</v>
+      </c>
+    </row>
+    <row r="149" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S149">
+        <v>1000</v>
+      </c>
+      <c r="T149">
+        <v>1</v>
+      </c>
+      <c r="U149">
+        <v>0.4</v>
+      </c>
+      <c r="V149">
+        <v>0.25</v>
+      </c>
+      <c r="W149">
+        <v>0.35</v>
+      </c>
+      <c r="X149" s="1">
+        <v>1880.6776</v>
+      </c>
+      <c r="Y149" s="1">
+        <v>1104.5425</v>
+      </c>
+      <c r="Z149" s="1">
+        <v>507.30493999999999</v>
+      </c>
+    </row>
+    <row r="150" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S150">
+        <v>1000</v>
+      </c>
+      <c r="T150">
+        <v>1</v>
+      </c>
+      <c r="U150">
+        <v>0.4</v>
+      </c>
+      <c r="V150">
+        <v>0.3</v>
+      </c>
+      <c r="W150">
+        <v>0.3</v>
+      </c>
+      <c r="X150" s="1">
+        <v>1910.9751000000001</v>
+      </c>
+      <c r="Y150" s="1">
+        <v>1040.3430000000001</v>
+      </c>
+      <c r="Z150" s="1">
+        <v>501.31065999999998</v>
+      </c>
+    </row>
+    <row r="151" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S151">
+        <v>1000</v>
+      </c>
+      <c r="T151">
+        <v>1</v>
+      </c>
+      <c r="U151">
+        <v>0.4</v>
+      </c>
+      <c r="V151">
+        <v>0.35</v>
+      </c>
+      <c r="W151">
+        <v>0.25</v>
+      </c>
+      <c r="X151" s="1">
+        <v>1940.9227000000001</v>
+      </c>
+      <c r="Y151" s="1">
+        <v>974.05661999999995</v>
+      </c>
+      <c r="Z151" s="1">
+        <v>494.84244000000001</v>
+      </c>
+    </row>
+    <row r="152" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S152">
+        <v>1000</v>
+      </c>
+      <c r="T152">
+        <v>1</v>
+      </c>
+      <c r="U152">
+        <v>0.4</v>
+      </c>
+      <c r="V152">
+        <v>0.4</v>
+      </c>
+      <c r="W152">
+        <v>0.2</v>
+      </c>
+      <c r="X152" s="1">
+        <v>1970.8698999999999</v>
+      </c>
+      <c r="Y152" s="1">
+        <v>903.97439999999995</v>
+      </c>
+      <c r="Z152" s="1">
+        <v>489.87123000000003</v>
+      </c>
+    </row>
+    <row r="153" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S153">
+        <v>1000</v>
+      </c>
+      <c r="T153">
+        <v>1</v>
+      </c>
+      <c r="U153">
+        <v>0.4</v>
+      </c>
+      <c r="V153">
+        <v>0.45</v>
+      </c>
+      <c r="W153">
+        <v>0.15</v>
+      </c>
+      <c r="X153" s="1">
+        <v>2001.1757</v>
+      </c>
+      <c r="Y153" s="1">
+        <v>826.69052999999997</v>
+      </c>
+      <c r="Z153" s="1">
+        <v>487.59625999999997</v>
+      </c>
+    </row>
+    <row r="154" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S154">
+        <v>1000</v>
+      </c>
+      <c r="T154">
+        <v>1</v>
+      </c>
+      <c r="U154">
+        <v>0.4</v>
+      </c>
+      <c r="V154">
+        <v>0.5</v>
+      </c>
+      <c r="W154">
+        <v>0.1</v>
+      </c>
+      <c r="X154" s="1">
+        <v>2032.2217000000001</v>
+      </c>
+      <c r="Y154" s="1">
+        <v>734.64903000000004</v>
+      </c>
+      <c r="Z154" s="1">
+        <v>488.66532000000001</v>
+      </c>
+    </row>
+    <row r="155" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S155">
+        <v>1000</v>
+      </c>
+      <c r="T155">
+        <v>1</v>
+      </c>
+      <c r="U155">
+        <v>0.4</v>
+      </c>
+      <c r="V155">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="W155">
+        <v>0.05</v>
+      </c>
+      <c r="X155" s="1">
+        <v>2064.4263000000001</v>
+      </c>
+      <c r="Y155" s="1">
+        <v>606.08074999999997</v>
+      </c>
+      <c r="Z155" s="1">
+        <v>493.35698000000002</v>
+      </c>
+    </row>
+    <row r="156" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S156">
+        <v>1000</v>
+      </c>
+      <c r="T156">
+        <v>1</v>
+      </c>
+      <c r="U156">
+        <v>0.4</v>
+      </c>
+      <c r="V156">
+        <v>0.6</v>
+      </c>
+      <c r="W156">
+        <v>0</v>
+      </c>
+      <c r="X156" s="1">
+        <v>2098.1587</v>
+      </c>
+      <c r="Y156" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z156" s="1">
+        <v>501.70889</v>
+      </c>
+    </row>
+    <row r="157" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S157">
+        <v>1000</v>
+      </c>
+      <c r="T157">
+        <v>1</v>
+      </c>
+      <c r="U157">
+        <v>0.45</v>
+      </c>
+      <c r="V157">
+        <v>0</v>
+      </c>
+      <c r="W157">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="X157" s="1">
+        <v>1907.364</v>
+      </c>
+      <c r="Y157" s="1">
+        <v>1283.8548000000001</v>
+      </c>
+      <c r="Z157" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S158">
+        <v>1000</v>
+      </c>
+      <c r="T158">
+        <v>1</v>
+      </c>
+      <c r="U158">
+        <v>0.45</v>
+      </c>
+      <c r="V158">
+        <v>0.05</v>
+      </c>
+      <c r="W158">
+        <v>0.5</v>
+      </c>
+      <c r="X158" s="1">
+        <v>1930.8714</v>
+      </c>
+      <c r="Y158" s="1">
+        <v>1205.2143000000001</v>
+      </c>
+      <c r="Z158" s="1">
+        <v>425.54131999999998</v>
+      </c>
+    </row>
+    <row r="159" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S159">
+        <v>1000</v>
+      </c>
+      <c r="T159">
+        <v>1</v>
+      </c>
+      <c r="U159">
+        <v>0.45</v>
+      </c>
+      <c r="V159">
+        <v>0.1</v>
+      </c>
+      <c r="W159">
+        <v>0.45</v>
+      </c>
+      <c r="X159" s="1">
+        <v>1957.8063999999999</v>
+      </c>
+      <c r="Y159" s="1">
+        <v>1131.2283</v>
+      </c>
+      <c r="Z159" s="1">
+        <v>453.75704999999999</v>
+      </c>
+    </row>
+    <row r="160" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S160">
+        <v>1000</v>
+      </c>
+      <c r="T160">
+        <v>1</v>
+      </c>
+      <c r="U160">
+        <v>0.45</v>
+      </c>
+      <c r="V160">
+        <v>0.15</v>
+      </c>
+      <c r="W160">
+        <v>0.4</v>
+      </c>
+      <c r="X160" s="1">
+        <v>1985.4703999999999</v>
+      </c>
+      <c r="Y160" s="1">
+        <v>1059.3533</v>
+      </c>
+      <c r="Z160" s="1">
+        <v>449.88260000000002</v>
+      </c>
+    </row>
+    <row r="161" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S161">
+        <v>1000</v>
+      </c>
+      <c r="T161">
+        <v>1</v>
+      </c>
+      <c r="U161">
+        <v>0.45</v>
+      </c>
+      <c r="V161">
+        <v>0.2</v>
+      </c>
+      <c r="W161">
+        <v>0.35</v>
+      </c>
+      <c r="X161" s="1">
+        <v>2013.2312999999999</v>
+      </c>
+      <c r="Y161" s="1">
+        <v>989.00161000000003</v>
+      </c>
+      <c r="Z161" s="1">
+        <v>434.63216</v>
+      </c>
+    </row>
+    <row r="162" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S162">
+        <v>1000</v>
+      </c>
+      <c r="T162">
+        <v>1</v>
+      </c>
+      <c r="U162">
+        <v>0.45</v>
+      </c>
+      <c r="V162">
+        <v>0.25</v>
+      </c>
+      <c r="W162">
+        <v>0.3</v>
+      </c>
+      <c r="X162" s="1">
+        <v>2040.9931999999999</v>
+      </c>
+      <c r="Y162" s="1">
+        <v>920.15930000000003</v>
+      </c>
+      <c r="Z162" s="1">
+        <v>416.83530999999999</v>
+      </c>
+    </row>
+    <row r="163" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S163">
+        <v>1000</v>
+      </c>
+      <c r="T163">
+        <v>1</v>
+      </c>
+      <c r="U163">
+        <v>0.45</v>
+      </c>
+      <c r="V163">
+        <v>0.3</v>
+      </c>
+      <c r="W163">
+        <v>0.25</v>
+      </c>
+      <c r="X163" s="1">
+        <v>2068.8525</v>
+      </c>
+      <c r="Y163" s="1">
+        <v>852.56538999999998</v>
+      </c>
+      <c r="Z163" s="1">
+        <v>400.88668000000001</v>
+      </c>
+    </row>
+    <row r="164" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S164">
+        <v>1000</v>
+      </c>
+      <c r="T164">
+        <v>1</v>
+      </c>
+      <c r="U164">
+        <v>0.45</v>
+      </c>
+      <c r="V164">
+        <v>0.35</v>
+      </c>
+      <c r="W164">
+        <v>0.2</v>
+      </c>
+      <c r="X164" s="1">
+        <v>2096.9888000000001</v>
+      </c>
+      <c r="Y164" s="1">
+        <v>784.86416999999994</v>
+      </c>
+      <c r="Z164" s="1">
+        <v>388.82288</v>
+      </c>
+    </row>
+    <row r="165" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S165">
+        <v>1000</v>
+      </c>
+      <c r="T165">
+        <v>1</v>
+      </c>
+      <c r="U165">
+        <v>0.45</v>
+      </c>
+      <c r="V165">
+        <v>0.4</v>
+      </c>
+      <c r="W165">
+        <v>0.15</v>
+      </c>
+      <c r="X165" s="1">
+        <v>2125.6259</v>
+      </c>
+      <c r="Y165" s="1">
+        <v>713.62787000000003</v>
+      </c>
+      <c r="Z165" s="1">
+        <v>381.41559000000001</v>
+      </c>
+    </row>
+    <row r="166" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S166">
+        <v>1000</v>
+      </c>
+      <c r="T166">
+        <v>1</v>
+      </c>
+      <c r="U166">
+        <v>0.45</v>
+      </c>
+      <c r="V166">
+        <v>0.45</v>
+      </c>
+      <c r="W166">
+        <v>0.1</v>
+      </c>
+      <c r="X166" s="1">
+        <v>2155.0167000000001</v>
+      </c>
+      <c r="Y166" s="1">
+        <v>631.40764000000001</v>
+      </c>
+      <c r="Z166" s="1">
+        <v>378.80399</v>
+      </c>
+    </row>
+    <row r="167" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S167">
+        <v>1000</v>
+      </c>
+      <c r="T167">
+        <v>1</v>
+      </c>
+      <c r="U167">
+        <v>0.45</v>
+      </c>
+      <c r="V167">
+        <v>0.5</v>
+      </c>
+      <c r="W167">
+        <v>0.05</v>
+      </c>
+      <c r="X167" s="1">
+        <v>2185.4299000000001</v>
+      </c>
+      <c r="Y167" s="1">
+        <v>518.39496999999994</v>
+      </c>
+      <c r="Z167" s="1">
+        <v>380.84116999999998</v>
+      </c>
+    </row>
+    <row r="168" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S168">
+        <v>1000</v>
+      </c>
+      <c r="T168">
+        <v>1</v>
+      </c>
+      <c r="U168">
+        <v>0.45</v>
+      </c>
+      <c r="V168">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="W168">
+        <v>0</v>
+      </c>
+      <c r="X168" s="1">
+        <v>2217.0410999999999</v>
+      </c>
+      <c r="Y168" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z168" s="1">
+        <v>387.26452999999998</v>
+      </c>
+    </row>
+    <row r="169" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S169">
+        <v>1000</v>
+      </c>
+      <c r="T169">
+        <v>1</v>
+      </c>
+      <c r="U169">
+        <v>0.5</v>
+      </c>
+      <c r="V169">
+        <v>0</v>
+      </c>
+      <c r="W169">
+        <v>0.5</v>
+      </c>
+      <c r="X169" s="1">
+        <v>2078.3393999999998</v>
+      </c>
+      <c r="Y169" s="1">
+        <v>1068.6233</v>
+      </c>
+      <c r="Z169" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S170">
+        <v>1000</v>
+      </c>
+      <c r="T170">
+        <v>1</v>
+      </c>
+      <c r="U170">
+        <v>0.5</v>
+      </c>
+      <c r="V170">
+        <v>0.05</v>
+      </c>
+      <c r="W170">
+        <v>0.45</v>
+      </c>
+      <c r="X170" s="1">
+        <v>2091.64</v>
+      </c>
+      <c r="Y170" s="1">
+        <v>979.86114999999995</v>
+      </c>
+      <c r="Z170" s="1">
+        <v>297.74164000000002</v>
+      </c>
+    </row>
+    <row r="171" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S171">
+        <v>1000</v>
+      </c>
+      <c r="T171">
+        <v>1</v>
+      </c>
+      <c r="U171">
+        <v>0.5</v>
+      </c>
+      <c r="V171">
+        <v>0.1</v>
+      </c>
+      <c r="W171">
+        <v>0.4</v>
+      </c>
+      <c r="X171" s="1">
+        <v>2111.3546000000001</v>
+      </c>
+      <c r="Y171" s="1">
+        <v>892.58884</v>
+      </c>
+      <c r="Z171" s="1">
+        <v>276.72741000000002</v>
+      </c>
+    </row>
+    <row r="172" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S172">
+        <v>1000</v>
+      </c>
+      <c r="T172">
+        <v>1</v>
+      </c>
+      <c r="U172">
+        <v>0.5</v>
+      </c>
+      <c r="V172">
+        <v>0.15</v>
+      </c>
+      <c r="W172">
+        <v>0.35</v>
+      </c>
+      <c r="X172" s="1">
+        <v>2133.6552999999999</v>
+      </c>
+      <c r="Y172" s="1">
+        <v>810.16705999999999</v>
+      </c>
+      <c r="Z172" s="1">
+        <v>231.48822000000001</v>
+      </c>
+    </row>
+    <row r="173" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S173">
+        <v>1000</v>
+      </c>
+      <c r="T173">
+        <v>1</v>
+      </c>
+      <c r="U173">
+        <v>0.5</v>
+      </c>
+      <c r="V173">
+        <v>0.2</v>
+      </c>
+      <c r="W173">
+        <v>0.3</v>
+      </c>
+      <c r="X173" s="1">
+        <v>2157.3253</v>
+      </c>
+      <c r="Y173" s="1">
+        <v>735.13697999999999</v>
+      </c>
+      <c r="Z173" s="1">
+        <v>176.00169</v>
+      </c>
+    </row>
+    <row r="174" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S174">
+        <v>1000</v>
+      </c>
+      <c r="T174">
+        <v>1</v>
+      </c>
+      <c r="U174">
+        <v>0.5</v>
+      </c>
+      <c r="V174">
+        <v>0.25</v>
+      </c>
+      <c r="W174">
+        <v>0.25</v>
+      </c>
+      <c r="X174" s="1">
+        <v>2181.9281000000001</v>
+      </c>
+      <c r="Y174" s="1">
+        <v>667.70077000000003</v>
+      </c>
+      <c r="Z174" s="1">
+        <v>113.78673999999999</v>
+      </c>
+    </row>
+    <row r="175" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S175">
+        <v>1000</v>
+      </c>
+      <c r="T175">
+        <v>1</v>
+      </c>
+      <c r="U175">
+        <v>0.5</v>
+      </c>
+      <c r="V175">
+        <v>0.3</v>
+      </c>
+      <c r="W175">
+        <v>0.2</v>
+      </c>
+      <c r="X175" s="1">
+        <v>2207.3386999999998</v>
+      </c>
+      <c r="Y175" s="1">
+        <v>604.86964</v>
+      </c>
+      <c r="Z175" s="1">
+        <v>41.948117000000003</v>
+      </c>
+    </row>
+    <row r="176" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S176">
+        <v>1000</v>
+      </c>
+      <c r="T176">
+        <v>1</v>
+      </c>
+      <c r="U176">
+        <v>0.5</v>
+      </c>
+      <c r="V176">
+        <v>0.35</v>
+      </c>
+      <c r="W176">
+        <v>0.15</v>
+      </c>
+      <c r="X176" s="1">
+        <v>2233.5783999999999</v>
+      </c>
+      <c r="Y176" s="1">
+        <v>540.66943000000003</v>
+      </c>
+      <c r="Z176" s="1">
+        <v>-48.273318000000003</v>
+      </c>
+    </row>
+    <row r="177" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S177">
+        <v>1000</v>
+      </c>
+      <c r="T177">
+        <v>1</v>
+      </c>
+      <c r="U177">
+        <v>0.5</v>
+      </c>
+      <c r="V177">
+        <v>0.4</v>
+      </c>
+      <c r="W177">
+        <v>0.1</v>
+      </c>
+      <c r="X177" s="1">
+        <v>2260.7440000000001</v>
+      </c>
+      <c r="Y177" s="1">
+        <v>465.00170000000003</v>
+      </c>
+      <c r="Z177" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S178">
+        <v>1000</v>
+      </c>
+      <c r="T178">
+        <v>1</v>
+      </c>
+      <c r="U178">
+        <v>0.5</v>
+      </c>
+      <c r="V178">
+        <v>0.45</v>
+      </c>
+      <c r="W178">
+        <v>0.05</v>
+      </c>
+      <c r="X178" s="1">
+        <v>2288.9598000000001</v>
+      </c>
+      <c r="Y178" s="1">
+        <v>354.83834000000002</v>
+      </c>
+      <c r="Z178" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S179">
+        <v>1000</v>
+      </c>
+      <c r="T179">
+        <v>1</v>
+      </c>
+      <c r="U179">
+        <v>0.5</v>
+      </c>
+      <c r="V179">
+        <v>0.5</v>
+      </c>
+      <c r="W179">
+        <v>0</v>
+      </c>
+      <c r="X179" s="1">
+        <v>2318.2710000000002</v>
+      </c>
+      <c r="Y179" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z179" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="180" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S180">
+        <v>1000</v>
+      </c>
+      <c r="T180">
+        <v>1</v>
+      </c>
+      <c r="U180">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="V180">
+        <v>0</v>
+      </c>
+      <c r="W180">
+        <v>0.45</v>
+      </c>
+      <c r="X180" s="1">
+        <v>2223.7818000000002</v>
+      </c>
+      <c r="Y180" s="1">
+        <v>618.41234999999995</v>
+      </c>
+      <c r="Z180" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S181">
+        <v>1000</v>
+      </c>
+      <c r="T181">
+        <v>1</v>
+      </c>
+      <c r="U181">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="V181">
+        <v>0.05</v>
+      </c>
+      <c r="W181">
+        <v>0.4</v>
+      </c>
+      <c r="X181" s="1">
+        <v>2230.0347999999999</v>
+      </c>
+      <c r="Y181" s="1">
+        <v>465.51071999999999</v>
+      </c>
+      <c r="Z181" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S182">
+        <v>1000</v>
+      </c>
+      <c r="T182">
+        <v>1</v>
+      </c>
+      <c r="U182">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="V182">
+        <v>0.1</v>
+      </c>
+      <c r="W182">
+        <v>0.35</v>
+      </c>
+      <c r="X182" s="1">
+        <v>2244.1931</v>
+      </c>
+      <c r="Y182" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z182" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S183">
+        <v>1000</v>
+      </c>
+      <c r="T183">
+        <v>1</v>
+      </c>
+      <c r="U183">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="V183">
+        <v>0.15</v>
+      </c>
+      <c r="W183">
+        <v>0.3</v>
+      </c>
+      <c r="X183" s="1">
+        <v>2262.1822000000002</v>
+      </c>
+      <c r="Y183" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z183" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="184" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S184">
+        <v>1000</v>
+      </c>
+      <c r="T184">
+        <v>1</v>
+      </c>
+      <c r="U184">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="V184">
+        <v>0.2</v>
+      </c>
+      <c r="W184">
+        <v>0.25</v>
+      </c>
+      <c r="X184" s="1">
+        <v>2282.4850000000001</v>
+      </c>
+      <c r="Y184" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z184" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S185">
+        <v>1000</v>
+      </c>
+      <c r="T185">
+        <v>1</v>
+      </c>
+      <c r="U185">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="V185">
+        <v>0.25</v>
+      </c>
+      <c r="W185">
+        <v>0.2</v>
+      </c>
+      <c r="X185" s="1">
+        <v>2304.4459999999999</v>
+      </c>
+      <c r="Y185" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z185" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S186">
+        <v>1000</v>
+      </c>
+      <c r="T186">
+        <v>1</v>
+      </c>
+      <c r="U186">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="V186">
+        <v>0.3</v>
+      </c>
+      <c r="W186">
+        <v>0.15</v>
+      </c>
+      <c r="X186" s="1">
+        <v>2327.7782000000002</v>
+      </c>
+      <c r="Y186" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z186" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S187">
+        <v>1000</v>
+      </c>
+      <c r="T187">
+        <v>1</v>
+      </c>
+      <c r="U187">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="V187">
+        <v>0.35</v>
+      </c>
+      <c r="W187">
+        <v>0.1</v>
+      </c>
+      <c r="X187" s="1">
+        <v>2352.3721</v>
+      </c>
+      <c r="Y187" s="1">
+        <v>-60.920009</v>
+      </c>
+      <c r="Z187" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="188" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S188">
+        <v>1000</v>
+      </c>
+      <c r="T188">
+        <v>1</v>
+      </c>
+      <c r="U188">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="V188">
+        <v>0.4</v>
+      </c>
+      <c r="W188">
+        <v>0.05</v>
+      </c>
+      <c r="X188" s="1">
+        <v>2378.1961000000001</v>
+      </c>
+      <c r="Y188" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z188" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S189">
+        <v>1000</v>
+      </c>
+      <c r="T189">
+        <v>1</v>
+      </c>
+      <c r="U189">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="V189">
+        <v>0.45</v>
+      </c>
+      <c r="W189">
+        <v>0</v>
+      </c>
+      <c r="X189" s="1">
+        <v>2405.1862999999998</v>
+      </c>
+      <c r="Y189" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z189" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="190" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S190">
+        <v>1000</v>
+      </c>
+      <c r="T190">
+        <v>1</v>
+      </c>
+      <c r="U190">
+        <v>0.6</v>
+      </c>
+      <c r="V190">
+        <v>0</v>
+      </c>
+      <c r="W190">
+        <v>0.4</v>
+      </c>
+      <c r="X190" s="1">
+        <v>2346.3150999999998</v>
+      </c>
+      <c r="Y190" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z190" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S191">
+        <v>1000</v>
+      </c>
+      <c r="T191">
+        <v>1</v>
+      </c>
+      <c r="U191">
+        <v>0.6</v>
+      </c>
+      <c r="V191">
+        <v>0.05</v>
+      </c>
+      <c r="W191">
+        <v>0.35</v>
+      </c>
+      <c r="X191" s="1">
+        <v>2348.2220000000002</v>
+      </c>
+      <c r="Y191" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z191" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S192">
+        <v>1000</v>
+      </c>
+      <c r="T192">
+        <v>1</v>
+      </c>
+      <c r="U192">
+        <v>0.6</v>
+      </c>
+      <c r="V192">
+        <v>0.1</v>
+      </c>
+      <c r="W192">
+        <v>0.3</v>
+      </c>
+      <c r="X192" s="1">
+        <v>2358.5056</v>
+      </c>
+      <c r="Y192" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z192" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S193">
+        <v>1000</v>
+      </c>
+      <c r="T193">
+        <v>1</v>
+      </c>
+      <c r="U193">
+        <v>0.6</v>
+      </c>
+      <c r="V193">
+        <v>0.15</v>
+      </c>
+      <c r="W193">
+        <v>0.25</v>
+      </c>
+      <c r="X193" s="1">
+        <v>2373.3323</v>
+      </c>
+      <c r="Y193" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z193" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S194">
+        <v>1000</v>
+      </c>
+      <c r="T194">
+        <v>1</v>
+      </c>
+      <c r="U194">
+        <v>0.6</v>
+      </c>
+      <c r="V194">
+        <v>0.2</v>
+      </c>
+      <c r="W194">
+        <v>0.2</v>
+      </c>
+      <c r="X194" s="1">
+        <v>2391.1014</v>
+      </c>
+      <c r="Y194" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z194" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S195">
+        <v>1000</v>
+      </c>
+      <c r="T195">
+        <v>1</v>
+      </c>
+      <c r="U195">
+        <v>0.6</v>
+      </c>
+      <c r="V195">
+        <v>0.25</v>
+      </c>
+      <c r="W195">
+        <v>0.15</v>
+      </c>
+      <c r="X195" s="1">
+        <v>2411.0435000000002</v>
+      </c>
+      <c r="Y195" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z195" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="196" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S196">
+        <v>1000</v>
+      </c>
+      <c r="T196">
+        <v>1</v>
+      </c>
+      <c r="U196">
+        <v>0.6</v>
+      </c>
+      <c r="V196">
+        <v>0.3</v>
+      </c>
+      <c r="W196">
+        <v>0.1</v>
+      </c>
+      <c r="X196" s="1">
+        <v>2432.7626</v>
+      </c>
+      <c r="Y196" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z196" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S197">
+        <v>1000</v>
+      </c>
+      <c r="T197">
+        <v>1</v>
+      </c>
+      <c r="U197">
+        <v>0.6</v>
+      </c>
+      <c r="V197">
+        <v>0.35</v>
+      </c>
+      <c r="W197">
+        <v>0.05</v>
+      </c>
+      <c r="X197" s="1">
+        <v>2456.0376999999999</v>
+      </c>
+      <c r="Y197" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z197" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S198">
+        <v>1000</v>
+      </c>
+      <c r="T198">
+        <v>1</v>
+      </c>
+      <c r="U198">
+        <v>0.6</v>
+      </c>
+      <c r="V198">
+        <v>0.4</v>
+      </c>
+      <c r="W198">
+        <v>0</v>
+      </c>
+      <c r="X198" s="1">
+        <v>2480.6875</v>
+      </c>
+      <c r="Y198" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z198" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="199" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S199">
+        <v>1000</v>
+      </c>
+      <c r="T199">
+        <v>1</v>
+      </c>
+      <c r="U199">
+        <v>0.65</v>
+      </c>
+      <c r="V199">
+        <v>0</v>
+      </c>
+      <c r="W199">
+        <v>0.35</v>
+      </c>
+      <c r="X199" s="1">
+        <v>2450.2276000000002</v>
+      </c>
+      <c r="Y199" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z199" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="200" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S200">
+        <v>1000</v>
+      </c>
+      <c r="T200">
+        <v>1</v>
+      </c>
+      <c r="U200">
+        <v>0.65</v>
+      </c>
+      <c r="V200">
+        <v>0.05</v>
+      </c>
+      <c r="W200">
+        <v>0.3</v>
+      </c>
+      <c r="X200" s="1">
+        <v>2449.6554999999998</v>
+      </c>
+      <c r="Y200" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z200" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S201">
+        <v>1000</v>
+      </c>
+      <c r="T201">
+        <v>1</v>
+      </c>
+      <c r="U201">
+        <v>0.65</v>
+      </c>
+      <c r="V201">
+        <v>0.1</v>
+      </c>
+      <c r="W201">
+        <v>0.25</v>
+      </c>
+      <c r="X201" s="1">
+        <v>2457.3948</v>
+      </c>
+      <c r="Y201" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z201" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="202" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S202">
+        <v>1000</v>
+      </c>
+      <c r="T202">
+        <v>1</v>
+      </c>
+      <c r="U202">
+        <v>0.65</v>
+      </c>
+      <c r="V202">
+        <v>0.15</v>
+      </c>
+      <c r="W202">
+        <v>0.2</v>
+      </c>
+      <c r="X202" s="1">
+        <v>2470.0279999999998</v>
+      </c>
+      <c r="Y202" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z202" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="203" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S203">
+        <v>1000</v>
+      </c>
+      <c r="T203">
+        <v>1</v>
+      </c>
+      <c r="U203">
+        <v>0.65</v>
+      </c>
+      <c r="V203">
+        <v>0.2</v>
+      </c>
+      <c r="W203">
+        <v>0.15</v>
+      </c>
+      <c r="X203" s="1">
+        <v>2485.9904999999999</v>
+      </c>
+      <c r="Y203" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z203" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="204" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S204">
+        <v>1000</v>
+      </c>
+      <c r="T204">
+        <v>1</v>
+      </c>
+      <c r="U204">
+        <v>0.65</v>
+      </c>
+      <c r="V204">
+        <v>0.25</v>
+      </c>
+      <c r="W204">
+        <v>0.1</v>
+      </c>
+      <c r="X204" s="1">
+        <v>2504.4652000000001</v>
+      </c>
+      <c r="Y204" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z204" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="205" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S205">
+        <v>1000</v>
+      </c>
+      <c r="T205">
+        <v>1</v>
+      </c>
+      <c r="U205">
+        <v>0.65</v>
+      </c>
+      <c r="V205">
+        <v>0.3</v>
+      </c>
+      <c r="W205">
+        <v>0.05</v>
+      </c>
+      <c r="X205" s="1">
+        <v>2524.9794999999999</v>
+      </c>
+      <c r="Y205" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z205" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="206" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S206">
+        <v>1000</v>
+      </c>
+      <c r="T206">
+        <v>1</v>
+      </c>
+      <c r="U206">
+        <v>0.65</v>
+      </c>
+      <c r="V206">
+        <v>0.35</v>
+      </c>
+      <c r="W206">
+        <v>0</v>
+      </c>
+      <c r="X206" s="1">
+        <v>2547.2026000000001</v>
+      </c>
+      <c r="Y206" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z206" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="207" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S207">
+        <v>1000</v>
+      </c>
+      <c r="T207">
+        <v>1</v>
+      </c>
+      <c r="U207">
+        <v>0.7</v>
+      </c>
+      <c r="V207">
+        <v>0</v>
+      </c>
+      <c r="W207">
+        <v>0.3</v>
+      </c>
+      <c r="X207" s="1">
+        <v>2539.4542999999999</v>
+      </c>
+      <c r="Y207" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z207" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="208" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S208">
+        <v>1000</v>
+      </c>
+      <c r="T208">
+        <v>1</v>
+      </c>
+      <c r="U208">
+        <v>0.7</v>
+      </c>
+      <c r="V208">
+        <v>0.05</v>
+      </c>
+      <c r="W208">
+        <v>0.25</v>
+      </c>
+      <c r="X208" s="1">
+        <v>2537.6165000000001</v>
+      </c>
+      <c r="Y208" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z208" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="209" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S209">
+        <v>1000</v>
+      </c>
+      <c r="T209">
+        <v>1</v>
+      </c>
+      <c r="U209">
+        <v>0.7</v>
+      </c>
+      <c r="V209">
+        <v>0.1</v>
+      </c>
+      <c r="W209">
+        <v>0.2</v>
+      </c>
+      <c r="X209" s="1">
+        <v>2543.7782000000002</v>
+      </c>
+      <c r="Y209" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z209" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="210" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S210">
+        <v>1000</v>
+      </c>
+      <c r="T210">
+        <v>1</v>
+      </c>
+      <c r="U210">
+        <v>0.7</v>
+      </c>
+      <c r="V210">
+        <v>0.15</v>
+      </c>
+      <c r="W210">
+        <v>0.15</v>
+      </c>
+      <c r="X210" s="1">
+        <v>2554.96</v>
+      </c>
+      <c r="Y210" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z210" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="211" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S211">
+        <v>1000</v>
+      </c>
+      <c r="T211">
+        <v>1</v>
+      </c>
+      <c r="U211">
+        <v>0.7</v>
+      </c>
+      <c r="V211">
+        <v>0.2</v>
+      </c>
+      <c r="W211">
+        <v>0.1</v>
+      </c>
+      <c r="X211" s="1">
+        <v>2569.6860000000001</v>
+      </c>
+      <c r="Y211" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z211" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="212" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S212">
+        <v>1000</v>
+      </c>
+      <c r="T212">
+        <v>1</v>
+      </c>
+      <c r="U212">
+        <v>0.7</v>
+      </c>
+      <c r="V212">
+        <v>0.25</v>
+      </c>
+      <c r="W212">
+        <v>0.05</v>
+      </c>
+      <c r="X212" s="1">
+        <v>2587.1251000000002</v>
+      </c>
+      <c r="Y212" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z212" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="213" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S213">
+        <v>1000</v>
+      </c>
+      <c r="T213">
+        <v>1</v>
+      </c>
+      <c r="U213">
+        <v>0.7</v>
+      </c>
+      <c r="V213">
+        <v>0.3</v>
+      </c>
+      <c r="W213">
+        <v>0</v>
+      </c>
+      <c r="X213" s="1">
+        <v>2606.7406999999998</v>
+      </c>
+      <c r="Y213" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z213" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S214">
+        <v>1000</v>
+      </c>
+      <c r="T214">
+        <v>1</v>
+      </c>
+      <c r="U214">
+        <v>0.75</v>
+      </c>
+      <c r="V214">
+        <v>0</v>
+      </c>
+      <c r="W214">
+        <v>0.25</v>
+      </c>
+      <c r="X214" s="1">
+        <v>2617.1012999999998</v>
+      </c>
+      <c r="Y214" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z214" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="215" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S215">
+        <v>1000</v>
+      </c>
+      <c r="T215">
+        <v>1</v>
+      </c>
+      <c r="U215">
+        <v>0.75</v>
+      </c>
+      <c r="V215">
+        <v>0.05</v>
+      </c>
+      <c r="W215">
+        <v>0.2</v>
+      </c>
+      <c r="X215" s="1">
+        <v>2614.7833000000001</v>
+      </c>
+      <c r="Y215" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z215" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="216" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S216">
+        <v>1000</v>
+      </c>
+      <c r="T216">
+        <v>1</v>
+      </c>
+      <c r="U216">
+        <v>0.75</v>
+      </c>
+      <c r="V216">
+        <v>0.1</v>
+      </c>
+      <c r="W216">
+        <v>0.15</v>
+      </c>
+      <c r="X216" s="1">
+        <v>2620.0540999999998</v>
+      </c>
+      <c r="Y216" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z216" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="217" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S217">
+        <v>1000</v>
+      </c>
+      <c r="T217">
+        <v>1</v>
+      </c>
+      <c r="U217">
+        <v>0.75</v>
+      </c>
+      <c r="V217">
+        <v>0.15</v>
+      </c>
+      <c r="W217">
+        <v>0.1</v>
+      </c>
+      <c r="X217" s="1">
+        <v>2630.3339999999998</v>
+      </c>
+      <c r="Y217" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z217" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="218" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S218">
+        <v>1000</v>
+      </c>
+      <c r="T218">
+        <v>1</v>
+      </c>
+      <c r="U218">
+        <v>0.75</v>
+      </c>
+      <c r="V218">
+        <v>0.2</v>
+      </c>
+      <c r="W218">
+        <v>0.05</v>
+      </c>
+      <c r="X218" s="1">
+        <v>2644.2505999999998</v>
+      </c>
+      <c r="Y218" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z218" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="219" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S219">
+        <v>1000</v>
+      </c>
+      <c r="T219">
+        <v>1</v>
+      </c>
+      <c r="U219">
+        <v>0.75</v>
+      </c>
+      <c r="V219">
+        <v>0.25</v>
+      </c>
+      <c r="W219">
+        <v>0</v>
+      </c>
+      <c r="X219" s="1">
+        <v>2660.9708999999998</v>
+      </c>
+      <c r="Y219" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z219" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="220" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S220">
+        <v>1000</v>
+      </c>
+      <c r="T220">
+        <v>1</v>
+      </c>
+      <c r="U220">
+        <v>0.8</v>
+      </c>
+      <c r="V220">
+        <v>0</v>
+      </c>
+      <c r="W220">
+        <v>0.2</v>
+      </c>
+      <c r="X220" s="1">
+        <v>2685.5142000000001</v>
+      </c>
+      <c r="Y220" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z220" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="221" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S221">
+        <v>1000</v>
+      </c>
+      <c r="T221">
+        <v>1</v>
+      </c>
+      <c r="U221">
+        <v>0.8</v>
+      </c>
+      <c r="V221">
+        <v>0.05</v>
+      </c>
+      <c r="W221">
+        <v>0.15</v>
+      </c>
+      <c r="X221" s="1">
+        <v>2683.2325999999998</v>
+      </c>
+      <c r="Y221" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z221" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="222" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S222">
+        <v>1000</v>
+      </c>
+      <c r="T222">
+        <v>1</v>
+      </c>
+      <c r="U222">
+        <v>0.8</v>
+      </c>
+      <c r="V222">
+        <v>0.1</v>
+      </c>
+      <c r="W222">
+        <v>0.1</v>
+      </c>
+      <c r="X222" s="1">
+        <v>2688.1008999999999</v>
+      </c>
+      <c r="Y222" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z222" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="223" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S223">
+        <v>1000</v>
+      </c>
+      <c r="T223">
+        <v>1</v>
+      </c>
+      <c r="U223">
+        <v>0.8</v>
+      </c>
+      <c r="V223">
+        <v>0.15</v>
+      </c>
+      <c r="W223">
+        <v>0.05</v>
+      </c>
+      <c r="X223" s="1">
+        <v>2697.8816000000002</v>
+      </c>
+      <c r="Y223" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z223" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="224" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S224">
+        <v>1000</v>
+      </c>
+      <c r="T224">
+        <v>1</v>
+      </c>
+      <c r="U224">
+        <v>0.8</v>
+      </c>
+      <c r="V224">
+        <v>0.2</v>
+      </c>
+      <c r="W224">
+        <v>0</v>
+      </c>
+      <c r="X224" s="1">
+        <v>2711.3000999999999</v>
+      </c>
+      <c r="Y224" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z224" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="225" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S225">
+        <v>1000</v>
+      </c>
+      <c r="T225">
+        <v>1</v>
+      </c>
+      <c r="U225">
+        <v>0.85</v>
+      </c>
+      <c r="V225">
+        <v>0</v>
+      </c>
+      <c r="W225">
+        <v>0.15</v>
+      </c>
+      <c r="X225" s="1">
+        <v>2746.4517000000001</v>
+      </c>
+      <c r="Y225" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z225" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S226">
+        <v>1000</v>
+      </c>
+      <c r="T226">
+        <v>1</v>
+      </c>
+      <c r="U226">
+        <v>0.85</v>
+      </c>
+      <c r="V226">
+        <v>0.05</v>
+      </c>
+      <c r="W226">
+        <v>0.1</v>
+      </c>
+      <c r="X226" s="1">
+        <v>2744.5535</v>
+      </c>
+      <c r="Y226" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z226" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S227">
+        <v>1000</v>
+      </c>
+      <c r="T227">
+        <v>1</v>
+      </c>
+      <c r="U227">
+        <v>0.85</v>
+      </c>
+      <c r="V227">
+        <v>0.1</v>
+      </c>
+      <c r="W227">
+        <v>0.05</v>
+      </c>
+      <c r="X227" s="1">
+        <v>2749.3692999999998</v>
+      </c>
+      <c r="Y227" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z227" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="228" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S228">
+        <v>1000</v>
+      </c>
+      <c r="T228">
+        <v>1</v>
+      </c>
+      <c r="U228">
+        <v>0.85</v>
+      </c>
+      <c r="V228">
+        <v>0.15</v>
+      </c>
+      <c r="W228">
+        <v>0</v>
+      </c>
+      <c r="X228" s="1">
+        <v>2758.9418999999998</v>
+      </c>
+      <c r="Y228" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z228" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S229">
+        <v>1000</v>
+      </c>
+      <c r="T229">
+        <v>1</v>
+      </c>
+      <c r="U229">
+        <v>0.9</v>
+      </c>
+      <c r="V229">
+        <v>0</v>
+      </c>
+      <c r="W229">
+        <v>0.1</v>
+      </c>
+      <c r="X229" s="1">
+        <v>2801.2435999999998</v>
+      </c>
+      <c r="Y229" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z229" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="230" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S230">
+        <v>1000</v>
+      </c>
+      <c r="T230">
+        <v>1</v>
+      </c>
+      <c r="U230">
+        <v>0.9</v>
+      </c>
+      <c r="V230">
+        <v>0.05</v>
+      </c>
+      <c r="W230">
+        <v>0.05</v>
+      </c>
+      <c r="X230" s="1">
+        <v>2799.9663</v>
+      </c>
+      <c r="Y230" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z230" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="231" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S231">
+        <v>1000</v>
+      </c>
+      <c r="T231">
+        <v>1</v>
+      </c>
+      <c r="U231">
+        <v>0.9</v>
+      </c>
+      <c r="V231">
+        <v>0.1</v>
+      </c>
+      <c r="W231">
+        <v>0</v>
+      </c>
+      <c r="X231" s="1">
+        <v>2804.9780999999998</v>
+      </c>
+      <c r="Y231" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z231" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S232">
+        <v>1000</v>
+      </c>
+      <c r="T232">
+        <v>1</v>
+      </c>
+      <c r="U232">
+        <v>0.95</v>
+      </c>
+      <c r="V232">
+        <v>0</v>
+      </c>
+      <c r="W232">
+        <v>0.05</v>
+      </c>
+      <c r="X232" s="1">
+        <v>2850.9088999999999</v>
+      </c>
+      <c r="Y232" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z232" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="233" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S233">
+        <v>1000</v>
+      </c>
+      <c r="T233">
+        <v>1</v>
+      </c>
+      <c r="U233">
+        <v>0.95</v>
+      </c>
+      <c r="V233">
+        <v>0.05</v>
+      </c>
+      <c r="W233">
+        <v>0</v>
+      </c>
+      <c r="X233" s="1">
+        <v>2850.4148</v>
+      </c>
+      <c r="Y233" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z233" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="234" spans="19:26" x14ac:dyDescent="0.35">
+      <c r="S234">
+        <v>1000</v>
+      </c>
+      <c r="T234">
+        <v>1</v>
+      </c>
+      <c r="U234">
+        <v>1</v>
+      </c>
+      <c r="V234">
+        <v>0</v>
+      </c>
+      <c r="W234">
+        <v>0</v>
+      </c>
+      <c r="X234" s="1">
+        <v>2896.2406000000001</v>
+      </c>
+      <c r="Y234" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z234" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
